--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AFD022-E879-42DB-97FC-3D7825B4C957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439511A-58E8-49AD-B994-EC125E2EEFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="508">
   <si>
     <t>Đời</t>
   </si>
@@ -954,309 +954,6 @@
     <t>đã ly hôn</t>
   </si>
   <si>
-    <t>VA-8.01.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.02.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.03.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.04.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.05.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.06.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.07.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.08.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.09.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.10.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.01.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.02.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.03.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.04.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.05.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.06.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.07.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.08.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.09.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.10.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.11.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.12.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.13.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.14.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.15.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.16.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.17.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.18.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.19.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.20.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.01.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.02.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.03.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.04.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.05.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.06.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.07.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.08.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.09.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.10.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.11.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.12.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.13.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.14.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.15.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.16.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.17.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.18.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.19.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.20.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.21.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.01.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.02.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.03.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.04.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.05.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.06.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.07.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.08.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.09.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.10.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.11.jpg</t>
-  </si>
-  <si>
-    <t>VA-11.12.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.01S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.02S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.03S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.04S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.05S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.07S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.08S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.09S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-8.10S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.02S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.03S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.04S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.05S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.06S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.07S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.08S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.09S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.10S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.11S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.12S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.13S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.14S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.15S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.16S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.17S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.18S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-9.19S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.01S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.02S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.02S2.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.03S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.04S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.05S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.06S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.08S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.10S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.09S1.jpg</t>
-  </si>
-  <si>
-    <t>VA-10.11S1.jpg</t>
-  </si>
-  <si>
     <t>Bà Lễ</t>
   </si>
   <si>
@@ -1269,9 +966,6 @@
     <t>Nhật</t>
   </si>
   <si>
-    <t>VA-11.08S1.jpg</t>
-  </si>
-  <si>
     <t>Dần</t>
   </si>
   <si>
@@ -1564,6 +1258,315 @@
   </si>
   <si>
     <t>chân dung 2</t>
+  </si>
+  <si>
+    <t>mất ngày 09/08/2026 tức 27/06</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.01.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.01S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.02.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.02S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.03.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.03S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.04.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.04S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.05.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.05S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.06.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.07.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.07S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.08.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.08S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.09.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.09S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.10.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-8.10S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.01.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.02.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.02S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.03.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.03S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.04.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.04S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.05.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.05S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.06.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.06S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.07.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.07S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.08.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.08S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.09.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.09S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.10.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.10S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.11.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.11S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.12.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.12S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.13.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.13S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.14.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.14S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.15.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.15S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.16.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.16S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.17.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.17S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.18.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.18S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.19.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.19S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-9.20.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.01.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.01S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.02.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.02S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.02S2.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.03.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.03S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.04.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.04S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.05.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.05S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.06.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.06S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.07.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.08.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.08S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.09.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.09S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.10.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.10S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.11.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.11S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.12.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.13.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.14.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.15.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.16.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.17.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.18.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.19.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.20.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-10.21.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.01.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.02.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.03.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.04.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.05.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.06.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.07.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.08.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.08S1.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.09.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.10.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.11.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/VA-11.12.jpg</t>
   </si>
 </sst>
 </file>
@@ -2091,18 +2094,18 @@
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
@@ -2132,7 +2135,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>451</v>
+        <v>349</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>119</v>
@@ -2306,7 +2309,7 @@
         <v>121</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>411</v>
+        <v>309</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>11</v>
@@ -2410,7 +2413,7 @@
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="M10" s="2">
         <v>5</v>
@@ -2445,7 +2448,7 @@
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="M11" s="2">
         <v>5</v>
@@ -2498,7 +2501,7 @@
         <v>245</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>412</v>
+        <v>310</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>11</v>
@@ -2542,7 +2545,7 @@
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="M14" s="2">
         <v>6</v>
@@ -2577,7 +2580,7 @@
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="M15" s="2">
         <v>6</v>
@@ -2610,7 +2613,7 @@
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>413</v>
+        <v>311</v>
       </c>
       <c r="M16" s="2">
         <v>6</v>
@@ -2770,7 +2773,7 @@
         <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>409</v>
+        <v>307</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
@@ -2904,7 +2907,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18" t="s">
-        <v>404</v>
+        <v>303</v>
       </c>
       <c r="M26" s="17">
         <v>7</v>
@@ -2915,13 +2918,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>175</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>415</v>
+        <v>313</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="17" t="s">
@@ -2933,7 +2936,7 @@
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18" t="s">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="M27" s="17">
         <v>7</v>
@@ -2966,7 +2969,7 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>449</v>
+        <v>347</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
@@ -3030,7 +3033,7 @@
         <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>303</v>
+        <v>406</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
@@ -3063,7 +3066,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="L31" s="18"/>
       <c r="M31" s="17">
@@ -3098,7 +3101,7 @@
         <v>205</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>304</v>
+        <v>408</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
@@ -3127,7 +3130,7 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18" t="s">
-        <v>367</v>
+        <v>409</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="17">
@@ -3162,7 +3165,7 @@
         <v>205</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>305</v>
+        <v>410</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
@@ -3193,7 +3196,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="L35" s="18"/>
       <c r="M35" s="17">
@@ -3218,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>418</v>
+        <v>316</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
@@ -3228,7 +3231,7 @@
         <v>205</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>306</v>
+        <v>412</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3">
@@ -3257,7 +3260,7 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="L37" s="18"/>
       <c r="M37" s="17">
@@ -3290,10 +3293,10 @@
         <v>205</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>307</v>
+        <v>414</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>422</v>
+        <v>320</v>
       </c>
       <c r="M38" s="3">
         <v>8</v>
@@ -3321,7 +3324,7 @@
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18" t="s">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="L39" s="18"/>
       <c r="M39" s="17">
@@ -3354,7 +3357,7 @@
         <v>205</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>308</v>
+        <v>416</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
@@ -3381,7 +3384,9 @@
       <c r="G41" s="3">
         <v>1944</v>
       </c>
-      <c r="H41" s="3"/>
+      <c r="H41" s="3">
+        <v>2026</v>
+      </c>
       <c r="I41" s="3" t="s">
         <v>34</v>
       </c>
@@ -3389,9 +3394,11 @@
         <v>205</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="L41" s="3"/>
+        <v>417</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>405</v>
+      </c>
       <c r="M41" s="3">
         <v>8</v>
       </c>
@@ -3420,7 +3427,7 @@
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18" t="s">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
@@ -3452,10 +3459,10 @@
         <v>34</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>310</v>
+        <v>419</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
@@ -3484,7 +3491,7 @@
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="L44" s="18"/>
       <c r="M44" s="17">
@@ -3514,13 +3521,13 @@
         <v>34</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>311</v>
+        <v>421</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>419</v>
+        <v>317</v>
       </c>
       <c r="M45" s="3">
         <v>8</v>
@@ -3548,7 +3555,7 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18" t="s">
-        <v>373</v>
+        <v>422</v>
       </c>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
@@ -3578,13 +3585,13 @@
         <v>34</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>312</v>
+        <v>423</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="M47" s="3">
         <v>8</v>
@@ -3612,7 +3619,7 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
@@ -3647,7 +3654,7 @@
         <v>207</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>313</v>
+        <v>425</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
@@ -3682,7 +3689,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>314</v>
+        <v>426</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
@@ -3711,7 +3718,7 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
       <c r="K51" s="18" t="s">
-        <v>375</v>
+        <v>427</v>
       </c>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
@@ -3748,7 +3755,7 @@
         <v>207</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>315</v>
+        <v>428</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
@@ -3779,7 +3786,7 @@
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18" t="s">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
@@ -3816,7 +3823,7 @@
         <v>207</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>316</v>
+        <v>430</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
@@ -3847,7 +3854,7 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18" t="s">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
@@ -3882,7 +3889,7 @@
         <v>207</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
@@ -3911,7 +3918,7 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="K57" s="18" t="s">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
@@ -3946,7 +3953,7 @@
         <v>207</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>318</v>
+        <v>434</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
@@ -3977,7 +3984,7 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18" t="s">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
@@ -4012,7 +4019,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>319</v>
+        <v>436</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
@@ -4043,7 +4050,7 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
@@ -4078,7 +4085,7 @@
         <v>207</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
@@ -4107,7 +4114,7 @@
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
       <c r="K63" s="18" t="s">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
@@ -4142,7 +4149,7 @@
         <v>208</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>321</v>
+        <v>440</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
@@ -4171,7 +4178,7 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18" t="s">
-        <v>382</v>
+        <v>441</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
@@ -4206,7 +4213,7 @@
         <v>208</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>322</v>
+        <v>442</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
@@ -4235,7 +4242,7 @@
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
       <c r="K67" s="18" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
@@ -4270,7 +4277,7 @@
         <v>208</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>323</v>
+        <v>444</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
@@ -4299,7 +4306,7 @@
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18" t="s">
-        <v>384</v>
+        <v>445</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
@@ -4334,7 +4341,7 @@
         <v>208</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>324</v>
+        <v>446</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
@@ -4363,7 +4370,7 @@
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18" t="s">
-        <v>385</v>
+        <v>447</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
@@ -4398,7 +4405,7 @@
         <v>208</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>325</v>
+        <v>448</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
@@ -4427,7 +4434,7 @@
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
@@ -4462,7 +4469,7 @@
         <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>326</v>
+        <v>450</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
@@ -4493,7 +4500,7 @@
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
       <c r="K75" s="18" t="s">
-        <v>387</v>
+        <v>451</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
@@ -4528,7 +4535,7 @@
         <v>212</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
@@ -4559,7 +4566,7 @@
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18" t="s">
-        <v>388</v>
+        <v>453</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
@@ -4594,7 +4601,7 @@
         <v>212</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>328</v>
+        <v>454</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
@@ -4623,7 +4630,7 @@
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
       <c r="K79" s="18" t="s">
-        <v>389</v>
+        <v>455</v>
       </c>
       <c r="L79" s="18"/>
       <c r="M79" s="17">
@@ -4658,7 +4665,7 @@
         <v>213</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>329</v>
+        <v>456</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
@@ -4687,7 +4694,7 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18" t="s">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
@@ -4722,7 +4729,7 @@
         <v>213</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>330</v>
+        <v>458</v>
       </c>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
@@ -4751,7 +4758,7 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
-        <v>391</v>
+        <v>459</v>
       </c>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
@@ -4786,7 +4793,7 @@
         <v>213</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>331</v>
+        <v>460</v>
       </c>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
@@ -4815,7 +4822,7 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
@@ -4848,10 +4855,10 @@
         <v>213</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>332</v>
+        <v>462</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>410</v>
+        <v>308</v>
       </c>
       <c r="M86" s="8">
         <v>9</v>
@@ -4885,7 +4892,7 @@
         <v>217</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>333</v>
+        <v>463</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
@@ -4916,7 +4923,7 @@
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
@@ -4951,7 +4958,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>334</v>
+        <v>465</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -4982,7 +4989,7 @@
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10" t="s">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
@@ -5013,7 +5020,7 @@
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="L91" s="10" t="s">
         <v>302</v>
@@ -5050,7 +5057,7 @@
         <v>217</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>335</v>
+        <v>468</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
@@ -5081,7 +5088,7 @@
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
-        <v>396</v>
+        <v>469</v>
       </c>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
@@ -5116,7 +5123,7 @@
         <v>218</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>336</v>
+        <v>470</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
@@ -5147,7 +5154,7 @@
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10" t="s">
-        <v>397</v>
+        <v>471</v>
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
@@ -5165,7 +5172,7 @@
         <v>181</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>421</v>
+        <v>319</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6" t="s">
@@ -5182,7 +5189,7 @@
         <v>218</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>337</v>
+        <v>472</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
@@ -5213,7 +5220,7 @@
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>398</v>
+        <v>473</v>
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
@@ -5248,7 +5255,7 @@
         <v>221</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>338</v>
+        <v>474</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
@@ -5279,7 +5286,7 @@
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
@@ -5314,7 +5321,7 @@
         <v>221</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
@@ -5349,7 +5356,7 @@
         <v>223</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>340</v>
+        <v>477</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
@@ -5380,7 +5387,7 @@
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10" t="s">
-        <v>400</v>
+        <v>478</v>
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
@@ -5415,7 +5422,7 @@
         <v>223</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>341</v>
+        <v>479</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
@@ -5446,7 +5453,7 @@
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10" t="s">
-        <v>402</v>
+        <v>480</v>
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
@@ -5481,7 +5488,7 @@
         <v>223</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>342</v>
+        <v>481</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
@@ -5512,7 +5519,7 @@
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10" t="s">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
@@ -5547,7 +5554,7 @@
         <v>224</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>343</v>
+        <v>483</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
@@ -5578,7 +5585,7 @@
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10" t="s">
-        <v>403</v>
+        <v>484</v>
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
@@ -5613,7 +5620,7 @@
         <v>224</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>344</v>
+        <v>485</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
@@ -5648,7 +5655,7 @@
         <v>228</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>345</v>
+        <v>486</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
@@ -5683,7 +5690,7 @@
         <v>228</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>346</v>
+        <v>487</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
@@ -5718,7 +5725,7 @@
         <v>229</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>347</v>
+        <v>488</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
@@ -5753,7 +5760,7 @@
         <v>229</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>348</v>
+        <v>489</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
@@ -5786,7 +5793,7 @@
         <v>231</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>349</v>
+        <v>490</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
@@ -5819,7 +5826,7 @@
         <v>231</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>350</v>
+        <v>491</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
@@ -5854,7 +5861,7 @@
         <v>232</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>351</v>
+        <v>492</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
@@ -5887,7 +5894,7 @@
         <v>232</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>352</v>
+        <v>493</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
@@ -5920,7 +5927,7 @@
         <v>232</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>353</v>
+        <v>494</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
@@ -5955,7 +5962,7 @@
         <v>234</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>354</v>
+        <v>495</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
@@ -5990,7 +5997,7 @@
         <v>234</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>355</v>
+        <v>496</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
@@ -6025,7 +6032,7 @@
         <v>235</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>356</v>
+        <v>497</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
@@ -6060,7 +6067,7 @@
         <v>235</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>357</v>
+        <v>498</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
@@ -6095,7 +6102,7 @@
         <v>237</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>358</v>
+        <v>499</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
@@ -6130,7 +6137,7 @@
         <v>237</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>359</v>
+        <v>500</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
@@ -6165,7 +6172,7 @@
         <v>240</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>360</v>
+        <v>501</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
@@ -6200,7 +6207,7 @@
         <v>240</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>361</v>
+        <v>502</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
@@ -6212,13 +6219,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>405</v>
+        <v>304</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9" t="s">
@@ -6231,7 +6238,7 @@
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="13" t="s">
-        <v>408</v>
+        <v>503</v>
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
@@ -6266,7 +6273,7 @@
         <v>242</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>362</v>
+        <v>504</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
@@ -6301,7 +6308,7 @@
         <v>242</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>363</v>
+        <v>505</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
@@ -6336,7 +6343,7 @@
         <v>243</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>364</v>
+        <v>506</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
@@ -6371,7 +6378,7 @@
         <v>243</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>365</v>
+        <v>507</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
@@ -6397,24 +6404,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>423</v>
+        <v>321</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>424</v>
+        <v>322</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>425</v>
+        <v>323</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>426</v>
+        <v>324</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>427</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>436</v>
+        <v>334</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>6</v>
@@ -6423,13 +6430,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>437</v>
+        <v>335</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>12</v>
@@ -6438,13 +6445,13 @@
         <v>196</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>16</v>
@@ -6453,13 +6460,13 @@
         <v>199</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>443</v>
+        <v>341</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>22</v>
@@ -6468,13 +6475,13 @@
         <v>200</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>463</v>
+        <v>361</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>202</v>
@@ -6483,13 +6490,13 @@
         <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>464</v>
+        <v>362</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>31</v>
@@ -6499,13 +6506,13 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>465</v>
+        <v>363</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>34</v>
@@ -6514,32 +6521,32 @@
         <v>205</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>444</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>466</v>
+        <v>364</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>416</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>467</v>
+        <v>365</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>36</v>
@@ -6548,13 +6555,13 @@
         <v>207</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>468</v>
+        <v>366</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>37</v>
@@ -6563,13 +6570,13 @@
         <v>208</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>469</v>
+        <v>367</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>38</v>
@@ -6578,13 +6585,13 @@
         <v>208</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>470</v>
+        <v>368</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>42</v>
@@ -6593,13 +6600,13 @@
         <v>212</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>471</v>
+        <v>369</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>43</v>
@@ -6608,13 +6615,13 @@
         <v>213</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>472</v>
+        <v>370</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>48</v>
@@ -6623,13 +6630,13 @@
         <v>217</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>473</v>
+        <v>371</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>49</v>
@@ -6638,13 +6645,13 @@
         <v>218</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>474</v>
+        <v>372</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>52</v>
@@ -6653,13 +6660,13 @@
         <v>221</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>475</v>
+        <v>373</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -6668,13 +6675,13 @@
         <v>223</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>476</v>
+        <v>374</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>55</v>
@@ -6683,13 +6690,13 @@
         <v>224</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>477</v>
+        <v>375</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>59</v>
@@ -6698,13 +6705,13 @@
         <v>228</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>478</v>
+        <v>376</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>60</v>
@@ -6713,13 +6720,13 @@
         <v>229</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>479</v>
+        <v>377</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>62</v>
@@ -6728,13 +6735,13 @@
         <v>231</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>480</v>
+        <v>378</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>63</v>
@@ -6743,13 +6750,13 @@
         <v>232</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>481</v>
+        <v>379</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>66</v>
@@ -6758,13 +6765,13 @@
         <v>234</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>482</v>
+        <v>380</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>68</v>
@@ -6773,15 +6780,15 @@
         <v>235</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>439</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>483</v>
+        <v>381</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>68</v>
@@ -6790,15 +6797,15 @@
         <v>300</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>438</v>
+        <v>336</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>440</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>484</v>
+        <v>382</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>70</v>
@@ -6807,13 +6814,13 @@
         <v>237</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>485</v>
+        <v>383</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>76</v>
@@ -6822,13 +6829,13 @@
         <v>240</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>486</v>
+        <v>384</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>78</v>
@@ -6837,13 +6844,13 @@
         <v>242</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>487</v>
+        <v>385</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>80</v>
@@ -6852,25 +6859,25 @@
         <v>243</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>488</v>
+        <v>386</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>405</v>
+        <v>304</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>108</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>439</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -6892,19 +6899,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>428</v>
+        <v>326</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>429</v>
+        <v>327</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>493</v>
+        <v>391</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>430</v>
+        <v>328</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>491</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -6912,33 +6919,33 @@
         <v>6</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>489</v>
+        <v>387</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>490</v>
+        <v>388</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>414</v>
+        <v>312</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>432</v>
+        <v>330</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>433</v>
+        <v>331</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6946,16 +6953,16 @@
         <v>36</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>495</v>
+        <v>393</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>500</v>
+        <v>398</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -6963,16 +6970,16 @@
         <v>207</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>494</v>
+        <v>392</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>501</v>
+        <v>399</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6980,16 +6987,16 @@
         <v>47</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>496</v>
+        <v>394</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>499</v>
+        <v>397</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6997,16 +7004,16 @@
         <v>48</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>497</v>
+        <v>395</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>498</v>
+        <v>396</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7014,16 +7021,16 @@
         <v>65</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>434</v>
+        <v>332</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>435</v>
+        <v>333</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>492</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7057,19 +7064,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>428</v>
+        <v>326</v>
       </c>
       <c r="B1" t="s">
-        <v>445</v>
+        <v>343</v>
       </c>
       <c r="C1" t="s">
-        <v>446</v>
+        <v>344</v>
       </c>
       <c r="D1" t="s">
-        <v>447</v>
+        <v>345</v>
       </c>
       <c r="E1" t="s">
-        <v>448</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7077,16 +7084,16 @@
         <v>68</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>459</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
-        <v>460</v>
+        <v>358</v>
       </c>
       <c r="D2" t="s">
-        <v>461</v>
+        <v>359</v>
       </c>
       <c r="E2" t="s">
-        <v>462</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -7108,19 +7115,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>452</v>
+        <v>350</v>
       </c>
       <c r="B1" t="s">
-        <v>502</v>
+        <v>400</v>
       </c>
       <c r="C1" t="s">
-        <v>453</v>
+        <v>351</v>
       </c>
       <c r="D1" t="s">
-        <v>503</v>
+        <v>401</v>
       </c>
       <c r="E1" t="s">
-        <v>454</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7128,16 +7135,16 @@
         <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>504</v>
+        <v>402</v>
       </c>
       <c r="C2" t="s">
-        <v>455</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>505</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
-        <v>456</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7145,16 +7152,16 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>504</v>
+        <v>402</v>
       </c>
       <c r="C3" t="s">
-        <v>458</v>
+        <v>356</v>
       </c>
       <c r="D3" t="s">
-        <v>506</v>
+        <v>404</v>
       </c>
       <c r="E3" t="s">
-        <v>457</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439511A-58E8-49AD-B994-EC125E2EEFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51607121-9B80-4238-8CAE-B538BE6D8C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="508">
   <si>
     <t>Đời</t>
   </si>
@@ -1104,18 +1104,12 @@
     <t>VISIBILITY</t>
   </si>
   <si>
-    <t>avatar.jpg</t>
-  </si>
-  <si>
     <t>public</t>
   </si>
   <si>
     <t>private</t>
   </si>
   <si>
-    <t>avatar2.jpg</t>
-  </si>
-  <si>
     <t>0389195050</t>
   </si>
   <si>
@@ -1567,6 +1561,12 @@
   </si>
   <si>
     <t>images/persons/VA-11.12.jpg</t>
+  </si>
+  <si>
+    <t>images/persons/CAOPHOVA807.jpg</t>
+  </si>
+  <si>
+    <t>Cáo Phó</t>
   </si>
 </sst>
 </file>
@@ -3033,7 +3033,7 @@
         <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
@@ -3066,7 +3066,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L31" s="18"/>
       <c r="M31" s="17">
@@ -3101,7 +3101,7 @@
         <v>205</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
@@ -3130,7 +3130,7 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="17">
@@ -3165,7 +3165,7 @@
         <v>205</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
@@ -3196,7 +3196,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L35" s="18"/>
       <c r="M35" s="17">
@@ -3231,7 +3231,7 @@
         <v>205</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3">
@@ -3260,7 +3260,7 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L37" s="18"/>
       <c r="M37" s="17">
@@ -3293,7 +3293,7 @@
         <v>205</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>320</v>
@@ -3324,7 +3324,7 @@
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L39" s="18"/>
       <c r="M39" s="17">
@@ -3357,7 +3357,7 @@
         <v>205</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
@@ -3394,10 +3394,10 @@
         <v>205</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M41" s="3">
         <v>8</v>
@@ -3427,7 +3427,7 @@
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
@@ -3462,7 +3462,7 @@
         <v>312</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
@@ -3491,7 +3491,7 @@
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L44" s="18"/>
       <c r="M44" s="17">
@@ -3524,7 +3524,7 @@
         <v>312</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>317</v>
@@ -3555,7 +3555,7 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
@@ -3588,7 +3588,7 @@
         <v>312</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>318</v>
@@ -3619,7 +3619,7 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
@@ -3654,7 +3654,7 @@
         <v>207</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
@@ -3689,7 +3689,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
@@ -3718,7 +3718,7 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
       <c r="K51" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
@@ -3755,7 +3755,7 @@
         <v>207</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
@@ -3786,7 +3786,7 @@
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
@@ -3823,7 +3823,7 @@
         <v>207</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
@@ -3854,7 +3854,7 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
@@ -3889,7 +3889,7 @@
         <v>207</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
@@ -3918,7 +3918,7 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="K57" s="18" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
@@ -3953,7 +3953,7 @@
         <v>207</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
@@ -3984,7 +3984,7 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
@@ -4019,7 +4019,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
@@ -4050,7 +4050,7 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
@@ -4085,7 +4085,7 @@
         <v>207</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
@@ -4114,7 +4114,7 @@
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
       <c r="K63" s="18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
@@ -4149,7 +4149,7 @@
         <v>208</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
@@ -4178,7 +4178,7 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
@@ -4213,7 +4213,7 @@
         <v>208</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
@@ -4242,7 +4242,7 @@
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
       <c r="K67" s="18" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
@@ -4277,7 +4277,7 @@
         <v>208</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
@@ -4306,7 +4306,7 @@
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
@@ -4341,7 +4341,7 @@
         <v>208</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
@@ -4370,7 +4370,7 @@
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
@@ -4405,7 +4405,7 @@
         <v>208</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
@@ -4434,7 +4434,7 @@
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
@@ -4469,7 +4469,7 @@
         <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
@@ -4500,7 +4500,7 @@
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
       <c r="K75" s="18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
@@ -4535,7 +4535,7 @@
         <v>212</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
@@ -4566,7 +4566,7 @@
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
@@ -4601,7 +4601,7 @@
         <v>212</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
@@ -4630,7 +4630,7 @@
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
       <c r="K79" s="18" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L79" s="18"/>
       <c r="M79" s="17">
@@ -4665,7 +4665,7 @@
         <v>213</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
@@ -4694,7 +4694,7 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
@@ -4729,7 +4729,7 @@
         <v>213</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
@@ -4758,7 +4758,7 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
@@ -4793,7 +4793,7 @@
         <v>213</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
@@ -4822,7 +4822,7 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
@@ -4855,7 +4855,7 @@
         <v>213</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>308</v>
@@ -4892,7 +4892,7 @@
         <v>217</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
@@ -4923,7 +4923,7 @@
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
@@ -4958,7 +4958,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -4989,7 +4989,7 @@
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
@@ -5020,7 +5020,7 @@
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L91" s="10" t="s">
         <v>302</v>
@@ -5057,7 +5057,7 @@
         <v>217</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
@@ -5088,7 +5088,7 @@
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
@@ -5123,7 +5123,7 @@
         <v>218</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
@@ -5154,7 +5154,7 @@
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
@@ -5189,7 +5189,7 @@
         <v>218</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
@@ -5220,7 +5220,7 @@
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
@@ -5255,7 +5255,7 @@
         <v>221</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
@@ -5286,7 +5286,7 @@
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
@@ -5321,7 +5321,7 @@
         <v>221</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
@@ -5356,7 +5356,7 @@
         <v>223</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
@@ -5387,7 +5387,7 @@
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
@@ -5422,7 +5422,7 @@
         <v>223</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
@@ -5453,7 +5453,7 @@
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
@@ -5488,7 +5488,7 @@
         <v>223</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
@@ -5519,7 +5519,7 @@
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
@@ -5554,7 +5554,7 @@
         <v>224</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
@@ -5585,7 +5585,7 @@
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
@@ -5620,7 +5620,7 @@
         <v>224</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
@@ -5655,7 +5655,7 @@
         <v>228</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
@@ -5690,7 +5690,7 @@
         <v>228</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
@@ -5725,7 +5725,7 @@
         <v>229</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
@@ -5760,7 +5760,7 @@
         <v>229</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
@@ -5793,7 +5793,7 @@
         <v>231</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
@@ -5826,7 +5826,7 @@
         <v>231</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
@@ -5861,7 +5861,7 @@
         <v>232</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
@@ -5894,7 +5894,7 @@
         <v>232</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
@@ -5927,7 +5927,7 @@
         <v>232</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
@@ -5962,7 +5962,7 @@
         <v>234</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
@@ -5997,7 +5997,7 @@
         <v>234</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
@@ -6029,10 +6029,10 @@
         <v>68</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
@@ -6067,7 +6067,7 @@
         <v>235</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
@@ -6102,7 +6102,7 @@
         <v>237</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
@@ -6137,7 +6137,7 @@
         <v>237</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
@@ -6172,7 +6172,7 @@
         <v>240</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
@@ -6207,7 +6207,7 @@
         <v>240</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
@@ -6238,7 +6238,7 @@
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
@@ -6273,7 +6273,7 @@
         <v>242</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
@@ -6308,7 +6308,7 @@
         <v>242</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
@@ -6343,7 +6343,7 @@
         <v>243</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
@@ -6378,7 +6378,7 @@
         <v>243</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
@@ -6481,7 +6481,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>202</v>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>31</v>
@@ -6512,7 +6512,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>34</v>
@@ -6529,7 +6529,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>34</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>36</v>
@@ -6561,7 +6561,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>37</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>38</v>
@@ -6591,7 +6591,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>42</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>43</v>
@@ -6621,7 +6621,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>48</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>49</v>
@@ -6651,7 +6651,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>52</v>
@@ -6666,7 +6666,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>55</v>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>59</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>60</v>
@@ -6726,7 +6726,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>62</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>63</v>
@@ -6756,7 +6756,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>66</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>68</v>
@@ -6788,7 +6788,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>68</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>70</v>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>76</v>
@@ -6835,7 +6835,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>78</v>
@@ -6850,7 +6850,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>80</v>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>304</v>
@@ -6905,13 +6905,13 @@
         <v>327</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>328</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -6922,13 +6922,13 @@
         <v>329</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6945,7 +6945,7 @@
         <v>331</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6956,13 +6956,13 @@
         <v>329</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -6973,13 +6973,13 @@
         <v>329</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6990,13 +6990,13 @@
         <v>329</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7007,13 +7007,13 @@
         <v>329</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7030,7 +7030,7 @@
         <v>333</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7084,16 +7084,16 @@
         <v>68</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" t="s">
         <v>357</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>358</v>
-      </c>
-      <c r="D2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E2" t="s">
-        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -7103,13 +7103,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2870D094-0F04-43A9-85F0-3281621B51DF}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7118,13 +7118,13 @@
         <v>350</v>
       </c>
       <c r="B1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C1" t="s">
         <v>351</v>
       </c>
       <c r="D1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E1" t="s">
         <v>352</v>
@@ -7135,16 +7135,16 @@
         <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E2" t="s">
         <v>353</v>
-      </c>
-      <c r="D2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E2" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7152,16 +7152,67 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="D3" t="s">
         <v>402</v>
       </c>
-      <c r="C3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D3" t="s">
-        <v>404</v>
-      </c>
       <c r="E3" t="s">
-        <v>355</v>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" t="s">
+        <v>507</v>
+      </c>
+      <c r="E6" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51607121-9B80-4238-8CAE-B538BE6D8C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B70C35-62DD-4E6B-8ACF-4C285513408D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="510">
   <si>
     <t>Đời</t>
   </si>
@@ -1038,15 +1038,9 @@
     <t>17/11</t>
   </si>
   <si>
-    <t>17/11 âm lịch</t>
-  </si>
-  <si>
     <t>23/07</t>
   </si>
   <si>
-    <t>23/07 âm lịch</t>
-  </si>
-  <si>
     <t>M0001</t>
   </si>
   <si>
@@ -1227,18 +1221,6 @@
     <t>28/08/2021</t>
   </si>
   <si>
-    <t>Mất 28/08/2015 thọ 68 tuổi</t>
-  </si>
-  <si>
-    <t>Mất 15/07/2021 thọ 66 tuổi</t>
-  </si>
-  <si>
-    <t>Mất 15/11/2014 thọ 89 tuổi</t>
-  </si>
-  <si>
-    <t>mất 04/10/1998 thọ 77 tuổi</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -1567,6 +1549,30 @@
   </si>
   <si>
     <t>Cáo Phó</t>
+  </si>
+  <si>
+    <t>27/06/2026</t>
+  </si>
+  <si>
+    <t>17/11 âm lịch , Giỗ cụ Quặm (vợ cụ Cốc)</t>
+  </si>
+  <si>
+    <t>Cụ Tích, Chết 15/11/2014 thọ 89 tuổi</t>
+  </si>
+  <si>
+    <t>Cụ Đương, Chết 04/10/1998 thọ 77 tuổi</t>
+  </si>
+  <si>
+    <t>Ông Độ, Chết 15/07/2021 thọ 66 tuổi</t>
+  </si>
+  <si>
+    <t>Ông Bích, Chết 28/08/2015 thọ 68 tuổi</t>
+  </si>
+  <si>
+    <t>Cụ Huệ, Chết Ngày 09/08/2026 tức  27/06/2026 Bính Ngọ,  thọ 83 tuổi</t>
+  </si>
+  <si>
+    <t>Thuỳ con cụ Chiến,  chết sớm, giỗ 23/07 âm lịch</t>
   </si>
 </sst>
 </file>
@@ -2085,6 +2091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05D1357-A17E-4B05-B803-B367BB9C049C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2105,7 +2112,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
@@ -2135,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>119</v>
@@ -2202,7 +2209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2262,7 +2269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2324,7 +2331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2384,7 +2391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2419,7 +2426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2454,7 +2461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2516,7 +2523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2551,7 +2558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2586,7 +2593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2646,7 +2653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2704,7 +2711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2762,7 +2769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2821,7 +2828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2852,7 +2859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2942,7 +2949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2969,7 +2976,7 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
@@ -3003,7 +3010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3033,7 +3040,7 @@
         <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
@@ -3066,14 +3073,14 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="L31" s="18"/>
       <c r="M31" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3101,7 +3108,7 @@
         <v>205</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
@@ -3130,14 +3137,14 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3165,7 +3172,7 @@
         <v>205</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
@@ -3196,14 +3203,14 @@
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="L35" s="18"/>
       <c r="M35" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3231,7 +3238,7 @@
         <v>205</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3">
@@ -3260,14 +3267,14 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="L37" s="18"/>
       <c r="M37" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3293,7 +3300,7 @@
         <v>205</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>320</v>
@@ -3324,14 +3331,14 @@
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L39" s="18"/>
       <c r="M39" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3357,14 +3364,14 @@
         <v>205</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3394,10 +3401,10 @@
         <v>205</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="M41" s="3">
         <v>8</v>
@@ -3427,14 +3434,14 @@
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3462,7 +3469,7 @@
         <v>312</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
@@ -3491,14 +3498,14 @@
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="L44" s="18"/>
       <c r="M44" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3524,7 +3531,7 @@
         <v>312</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>317</v>
@@ -3555,14 +3562,14 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3588,7 +3595,7 @@
         <v>312</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>318</v>
@@ -3619,14 +3626,14 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -3654,14 +3661,14 @@
         <v>207</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -3689,7 +3696,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
@@ -3718,14 +3725,14 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
       <c r="K51" s="18" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3755,7 +3762,7 @@
         <v>207</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
@@ -3786,14 +3793,14 @@
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -3823,7 +3830,7 @@
         <v>207</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
@@ -3854,14 +3861,14 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -3889,7 +3896,7 @@
         <v>207</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
@@ -3918,14 +3925,14 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="K57" s="18" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -3953,7 +3960,7 @@
         <v>207</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
@@ -3984,14 +3991,14 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -4019,7 +4026,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
@@ -4050,14 +4057,14 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -4085,7 +4092,7 @@
         <v>207</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
@@ -4114,14 +4121,14 @@
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
       <c r="K63" s="18" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -4149,7 +4156,7 @@
         <v>208</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
@@ -4178,14 +4185,14 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -4213,7 +4220,7 @@
         <v>208</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
@@ -4242,14 +4249,14 @@
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
       <c r="K67" s="18" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -4277,7 +4284,7 @@
         <v>208</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
@@ -4306,14 +4313,14 @@
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -4341,7 +4348,7 @@
         <v>208</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
@@ -4370,14 +4377,14 @@
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -4405,7 +4412,7 @@
         <v>208</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
@@ -4434,14 +4441,14 @@
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -4469,7 +4476,7 @@
         <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
@@ -4500,14 +4507,14 @@
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
       <c r="K75" s="18" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -4535,7 +4542,7 @@
         <v>212</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
@@ -4566,14 +4573,14 @@
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -4601,7 +4608,7 @@
         <v>212</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
@@ -4630,14 +4637,14 @@
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
       <c r="K79" s="18" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="L79" s="18"/>
       <c r="M79" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -4665,7 +4672,7 @@
         <v>213</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
@@ -4694,14 +4701,14 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="22">
         <v>81</v>
       </c>
@@ -4729,7 +4736,7 @@
         <v>213</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
@@ -4758,14 +4765,14 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>83</v>
       </c>
@@ -4793,7 +4800,7 @@
         <v>213</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
@@ -4822,14 +4829,14 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>85</v>
       </c>
@@ -4855,7 +4862,7 @@
         <v>213</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>308</v>
@@ -4864,7 +4871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -4892,7 +4899,7 @@
         <v>217</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
@@ -4923,14 +4930,14 @@
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -4958,7 +4965,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -4989,7 +4996,7 @@
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
@@ -5020,7 +5027,7 @@
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="L91" s="10" t="s">
         <v>302</v>
@@ -5029,7 +5036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>91</v>
       </c>
@@ -5057,7 +5064,7 @@
         <v>217</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
@@ -5088,14 +5095,14 @@
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>93</v>
       </c>
@@ -5123,7 +5130,7 @@
         <v>218</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
@@ -5154,14 +5161,14 @@
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>95</v>
       </c>
@@ -5189,7 +5196,7 @@
         <v>218</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
@@ -5220,14 +5227,14 @@
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -5255,7 +5262,7 @@
         <v>221</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
@@ -5286,14 +5293,14 @@
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>99</v>
       </c>
@@ -5321,14 +5328,14 @@
         <v>221</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>100</v>
       </c>
@@ -5356,7 +5363,7 @@
         <v>223</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
@@ -5387,14 +5394,14 @@
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -5422,7 +5429,7 @@
         <v>223</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
@@ -5453,14 +5460,14 @@
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -5488,7 +5495,7 @@
         <v>223</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
@@ -5519,14 +5526,14 @@
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -5554,7 +5561,7 @@
         <v>224</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
@@ -5585,14 +5592,14 @@
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -5620,14 +5627,14 @@
         <v>224</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -5655,14 +5662,14 @@
         <v>228</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -5690,14 +5697,14 @@
         <v>228</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>111</v>
       </c>
@@ -5725,14 +5732,14 @@
         <v>229</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -5760,14 +5767,14 @@
         <v>229</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>113</v>
       </c>
@@ -5793,14 +5800,14 @@
         <v>231</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -5826,14 +5833,14 @@
         <v>231</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -5861,14 +5868,14 @@
         <v>232</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -5894,14 +5901,14 @@
         <v>232</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>117</v>
       </c>
@@ -5927,14 +5934,14 @@
         <v>232</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>118</v>
       </c>
@@ -5962,14 +5969,14 @@
         <v>234</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>119</v>
       </c>
@@ -5997,14 +6004,14 @@
         <v>234</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -6032,14 +6039,14 @@
         <v>300</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -6067,14 +6074,14 @@
         <v>235</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -6102,14 +6109,14 @@
         <v>237</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>123</v>
       </c>
@@ -6137,14 +6144,14 @@
         <v>237</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>124</v>
       </c>
@@ -6172,14 +6179,14 @@
         <v>240</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>125</v>
       </c>
@@ -6207,7 +6214,7 @@
         <v>240</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
@@ -6238,14 +6245,14 @@
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="13" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>127</v>
       </c>
@@ -6273,14 +6280,14 @@
         <v>242</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>128</v>
       </c>
@@ -6308,14 +6315,14 @@
         <v>242</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>129</v>
       </c>
@@ -6343,14 +6350,14 @@
         <v>243</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>130</v>
       </c>
@@ -6378,7 +6385,7 @@
         <v>243</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
@@ -6386,7 +6393,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M131" xr:uid="{B05D1357-A17E-4B05-B803-B367BB9C049C}"/>
+  <autoFilter ref="A1:M131" xr:uid="{B05D1357-A17E-4B05-B803-B367BB9C049C}">
+    <filterColumn colId="8">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6421,7 +6432,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>6</v>
@@ -6430,13 +6441,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>12</v>
@@ -6445,13 +6456,13 @@
         <v>196</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>16</v>
@@ -6460,13 +6471,13 @@
         <v>199</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>22</v>
@@ -6475,13 +6486,13 @@
         <v>200</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>202</v>
@@ -6490,13 +6501,13 @@
         <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>31</v>
@@ -6506,13 +6517,13 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>34</v>
@@ -6521,15 +6532,15 @@
         <v>205</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>34</v>
@@ -6538,7 +6549,7 @@
         <v>312</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>314</v>
@@ -6546,7 +6557,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>36</v>
@@ -6555,13 +6566,13 @@
         <v>207</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>37</v>
@@ -6570,28 +6581,28 @@
         <v>208</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>42</v>
@@ -6600,13 +6611,13 @@
         <v>212</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>43</v>
@@ -6615,13 +6626,13 @@
         <v>213</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>48</v>
@@ -6630,13 +6641,13 @@
         <v>217</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>49</v>
@@ -6645,13 +6656,13 @@
         <v>218</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>52</v>
@@ -6660,13 +6671,13 @@
         <v>221</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -6675,13 +6686,13 @@
         <v>223</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>55</v>
@@ -6690,13 +6701,13 @@
         <v>224</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>59</v>
@@ -6705,13 +6716,13 @@
         <v>228</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>60</v>
@@ -6720,13 +6731,13 @@
         <v>229</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>62</v>
@@ -6735,13 +6746,13 @@
         <v>231</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>63</v>
@@ -6750,13 +6761,13 @@
         <v>232</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>66</v>
@@ -6765,13 +6776,13 @@
         <v>234</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>68</v>
@@ -6780,15 +6791,15 @@
         <v>235</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>68</v>
@@ -6797,15 +6808,15 @@
         <v>300</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>336</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>70</v>
@@ -6814,13 +6825,13 @@
         <v>237</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>76</v>
@@ -6829,13 +6840,13 @@
         <v>240</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>78</v>
@@ -6844,13 +6855,13 @@
         <v>242</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>80</v>
@@ -6859,13 +6870,13 @@
         <v>243</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>304</v>
@@ -6874,10 +6885,10 @@
         <v>108</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -6893,7 +6904,7 @@
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="4" max="4" width="61.5703125" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6905,13 +6916,13 @@
         <v>327</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>328</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -6922,13 +6933,13 @@
         <v>329</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6942,10 +6953,10 @@
         <v>330</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>331</v>
+        <v>503</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6956,13 +6967,13 @@
         <v>329</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>396</v>
+        <v>504</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -6973,13 +6984,13 @@
         <v>329</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>397</v>
+        <v>505</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6990,13 +7001,13 @@
         <v>329</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>395</v>
+        <v>506</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7007,13 +7018,13 @@
         <v>329</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>394</v>
+        <v>507</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7024,21 +7035,31 @@
         <v>329</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>333</v>
+        <v>509</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>386</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{1A337F81-5FE2-493C-AFA8-0A38C4915F5A}">
@@ -7067,16 +7088,16 @@
         <v>326</v>
       </c>
       <c r="B1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1" t="s">
         <v>343</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>344</v>
-      </c>
-      <c r="D1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7084,16 +7105,16 @@
         <v>68</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" t="s">
         <v>355</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>356</v>
-      </c>
-      <c r="D2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E2" t="s">
-        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -7115,19 +7136,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E1" t="s">
         <v>350</v>
-      </c>
-      <c r="B1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7135,16 +7156,16 @@
         <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7152,16 +7173,16 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7169,16 +7190,16 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7186,16 +7207,16 @@
         <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D5" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7203,16 +7224,16 @@
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D6" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B70C35-62DD-4E6B-8ACF-4C285513408D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF538CE6-4C0A-4392-A4E4-E3CA04D8A860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="MEDIA" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">EVENTS!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">EVENTS!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PERSONS!$A$1:$M$131</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="545">
   <si>
     <t>Đời</t>
   </si>
@@ -954,9 +954,6 @@
     <t>đã ly hôn</t>
   </si>
   <si>
-    <t>Bà Lễ</t>
-  </si>
-  <si>
     <t>VA-11.08S1</t>
   </si>
   <si>
@@ -1197,9 +1194,6 @@
     <t>30/05</t>
   </si>
   <si>
-    <t>Giỗ cụ thuỷ tổ</t>
-  </si>
-  <si>
     <t>MỘ PHẦN</t>
   </si>
   <si>
@@ -1554,25 +1548,136 @@
     <t>27/06/2026</t>
   </si>
   <si>
-    <t>17/11 âm lịch , Giỗ cụ Quặm (vợ cụ Cốc)</t>
-  </si>
-  <si>
-    <t>Cụ Tích, Chết 15/11/2014 thọ 89 tuổi</t>
-  </si>
-  <si>
     <t>Cụ Đương, Chết 04/10/1998 thọ 77 tuổi</t>
   </si>
   <si>
-    <t>Ông Độ, Chết 15/07/2021 thọ 66 tuổi</t>
-  </si>
-  <si>
-    <t>Ông Bích, Chết 28/08/2015 thọ 68 tuổi</t>
-  </si>
-  <si>
-    <t>Cụ Huệ, Chết Ngày 09/08/2026 tức  27/06/2026 Bính Ngọ,  thọ 83 tuổi</t>
-  </si>
-  <si>
-    <t>Thuỳ con cụ Chiến,  chết sớm, giỗ 23/07 âm lịch</t>
+    <t>08/08</t>
+  </si>
+  <si>
+    <t>Giỗ Cụ Ngô Quý Thị, Hiệu Từ Liễn</t>
+  </si>
+  <si>
+    <t>Giỗ cụ Thuỷ Tổ. Tự Phúc Bằng</t>
+  </si>
+  <si>
+    <t>15/02</t>
+  </si>
+  <si>
+    <t>Giỗ cụ bà Nguyễn Thị Hoa, hiệu Diệu Quang</t>
+  </si>
+  <si>
+    <t>Phúc Tuất</t>
+  </si>
+  <si>
+    <t>Phúc Tích</t>
+  </si>
+  <si>
+    <t>Phúc Đào</t>
+  </si>
+  <si>
+    <t>Phúc Thảo</t>
+  </si>
+  <si>
+    <t>Phúc Định</t>
+  </si>
+  <si>
+    <t>13/08</t>
+  </si>
+  <si>
+    <t>Giỗ cụ Nguyễn Quý Công , Tự Phúc Tuất</t>
+  </si>
+  <si>
+    <t>Xuân Thuỳ con cụ Chiến,  chết sớm, giỗ 23/07 âm lịch</t>
+  </si>
+  <si>
+    <t>Ông Độ, Pháp danh Minh Phúc, Chết 15/07/2021 thọ 66 tuổi</t>
+  </si>
+  <si>
+    <t>23/02</t>
+  </si>
+  <si>
+    <t>Cụ Huệ, Chết ngày 09/08/2026 tức  27/06/2026 Bính Ngọ,  thọ 83 tuổi</t>
+  </si>
+  <si>
+    <t>03/06</t>
+  </si>
+  <si>
+    <t>Cụ Phúc Thảo,  pháp danh Minh Hiền</t>
+  </si>
+  <si>
+    <t>Cụ Phúc Tích, Chết 15/11/2014 thọ 89 tuổi</t>
+  </si>
+  <si>
+    <t>29/01</t>
+  </si>
+  <si>
+    <t>cụ Phúc Đào, pháp danh Liễu Ngộ</t>
+  </si>
+  <si>
+    <t>29/04</t>
+  </si>
+  <si>
+    <t>22/11/2018</t>
+  </si>
+  <si>
+    <t>cụ Bà Chiến, Pháp Danh Diệu Hải</t>
+  </si>
+  <si>
+    <t>Cụ Bà Đào, Pháp danh Diệu Hà,</t>
+  </si>
+  <si>
+    <t>cụ bà Quặm (vợ lẽ cụ Cốc) Giỗ 17/11 âm lịch</t>
+  </si>
+  <si>
+    <t>Nguyễn Phúc Lan, Tự Thuần Tuệ  (chết trẻ )</t>
+  </si>
+  <si>
+    <t>Ông Bích, Pháp danh Minh Định, Chết 28/08/2021 thọ 68 tuổi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">con tên Xuân Phong, Phương, Phú </t>
+  </si>
+  <si>
+    <t>Bà Lễ, Giỗ 14/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giỗ </t>
+  </si>
+  <si>
+    <t>14/12</t>
+  </si>
+  <si>
+    <t>cụ Bào, vợ cụ Cốc</t>
+  </si>
+  <si>
+    <t>Tự Thuần Ban, giỗ 15/10 ?</t>
+  </si>
+  <si>
+    <t>Giỗ 15/07 ?</t>
+  </si>
+  <si>
+    <t>tên Tự : Thuần Bản ( theo ds cúng giỗ) ?</t>
+  </si>
+  <si>
+    <t>Vũ Thị Vạc, hiệu Diệu Đài giỗ 02/02 ?</t>
+  </si>
+  <si>
+    <t>15/10</t>
+  </si>
+  <si>
+    <t>Tự Thuần Ban  giỗ 15/10 (chép theo danh sách Cung Thỉnh)</t>
+  </si>
+  <si>
+    <t>ThuTuHienThi</t>
+  </si>
+  <si>
+    <t>Giỗ 12/11</t>
+  </si>
+  <si>
+    <t>12/11</t>
+  </si>
+  <si>
+    <t>Nguyễn Quý Công Tự Phúc Cốc</t>
   </si>
 </sst>
 </file>
@@ -1682,7 +1787,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1744,11 +1849,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1774,9 +1892,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2091,7 +2212,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05D1357-A17E-4B05-B803-B367BB9C049C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2112,7 +2232,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
@@ -2142,7 +2262,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>119</v>
@@ -2209,7 +2329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2269,7 +2389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2316,7 +2436,7 @@
         <v>121</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>11</v>
@@ -2326,12 +2446,14 @@
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
+      <c r="L7" s="18" t="s">
+        <v>536</v>
+      </c>
       <c r="M7" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2359,7 +2481,9 @@
         <v>9</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -2391,7 +2515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2420,13 +2544,13 @@
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M10" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2455,13 +2579,13 @@
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M11" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2489,7 +2613,9 @@
         <v>9</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>535</v>
+      </c>
       <c r="M12" s="2">
         <v>5</v>
       </c>
@@ -2508,7 +2634,7 @@
         <v>245</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>11</v>
@@ -2523,7 +2649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2552,13 +2678,13 @@
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M14" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2587,13 +2713,13 @@
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M15" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2620,7 +2746,7 @@
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M16" s="2">
         <v>6</v>
@@ -2653,7 +2779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2699,7 +2825,7 @@
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="18"/>
@@ -2711,7 +2837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2724,7 +2850,9 @@
       <c r="D20" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>507</v>
+      </c>
       <c r="F20" s="2" t="s">
         <v>8</v>
       </c>
@@ -2764,12 +2892,14 @@
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
+      <c r="L21" s="18" t="s">
+        <v>538</v>
+      </c>
       <c r="M21" s="17">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2780,7 +2910,7 @@
         <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
@@ -2828,7 +2958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2859,7 +2989,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2886,7 +3016,9 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="L25" s="2" t="s">
+        <v>542</v>
+      </c>
       <c r="M25" s="2">
         <v>7</v>
       </c>
@@ -2914,7 +3046,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18" t="s">
-        <v>303</v>
+        <v>531</v>
       </c>
       <c r="M26" s="17">
         <v>7</v>
@@ -2925,13 +3057,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>175</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="17" t="s">
@@ -2943,13 +3075,13 @@
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M27" s="17">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2976,7 +3108,7 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
@@ -3010,7 +3142,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3023,7 +3155,9 @@
       <c r="D30" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>508</v>
+      </c>
       <c r="F30" s="3" t="s">
         <v>8</v>
       </c>
@@ -3040,7 +3174,7 @@
         <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
@@ -3073,14 +3207,14 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L31" s="18"/>
       <c r="M31" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3093,7 +3227,9 @@
       <c r="D32" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>509</v>
+      </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3108,7 +3244,7 @@
         <v>205</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
@@ -3137,14 +3273,14 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3157,7 +3293,9 @@
       <c r="D34" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>510</v>
+      </c>
       <c r="F34" s="3" t="s">
         <v>8</v>
       </c>
@@ -3172,7 +3310,7 @@
         <v>205</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
@@ -3203,14 +3341,14 @@
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L35" s="18"/>
       <c r="M35" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3223,12 +3361,14 @@
       <c r="D36" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
@@ -3238,9 +3378,11 @@
         <v>205</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="L36" s="3"/>
+        <v>402</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>530</v>
+      </c>
       <c r="M36" s="3">
         <v>8</v>
       </c>
@@ -3267,14 +3409,14 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L37" s="18"/>
       <c r="M37" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3300,10 +3442,10 @@
         <v>205</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M38" s="3">
         <v>8</v>
@@ -3331,14 +3473,14 @@
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L39" s="18"/>
       <c r="M39" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3364,14 +3506,14 @@
         <v>205</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3401,10 +3543,10 @@
         <v>205</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M41" s="3">
         <v>8</v>
@@ -3434,14 +3576,14 @@
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3466,10 +3608,10 @@
         <v>34</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
@@ -3498,14 +3640,14 @@
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L44" s="18"/>
       <c r="M44" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3528,13 +3670,13 @@
         <v>34</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M45" s="3">
         <v>8</v>
@@ -3562,14 +3704,14 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3592,13 +3734,13 @@
         <v>34</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M47" s="3">
         <v>8</v>
@@ -3626,14 +3768,14 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -3661,14 +3803,14 @@
         <v>207</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -3696,7 +3838,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
@@ -3725,14 +3867,14 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
       <c r="K51" s="18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3762,7 +3904,7 @@
         <v>207</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
@@ -3793,14 +3935,14 @@
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -3830,7 +3972,7 @@
         <v>207</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
@@ -3861,14 +4003,14 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -3896,7 +4038,7 @@
         <v>207</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
@@ -3925,14 +4067,14 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="K57" s="18" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -3960,7 +4102,7 @@
         <v>207</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
@@ -3991,14 +4133,14 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -4026,7 +4168,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
@@ -4057,14 +4199,14 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -4092,7 +4234,7 @@
         <v>207</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
@@ -4121,14 +4263,14 @@
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
       <c r="K63" s="18" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -4156,7 +4298,7 @@
         <v>208</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
@@ -4185,14 +4327,14 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -4220,7 +4362,7 @@
         <v>208</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
@@ -4249,14 +4391,14 @@
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
       <c r="K67" s="18" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -4284,7 +4426,7 @@
         <v>208</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
@@ -4313,14 +4455,14 @@
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -4348,7 +4490,7 @@
         <v>208</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
@@ -4377,14 +4519,14 @@
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -4412,7 +4554,7 @@
         <v>208</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
@@ -4441,14 +4583,14 @@
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -4476,7 +4618,7 @@
         <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
@@ -4507,14 +4649,14 @@
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
       <c r="K75" s="18" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -4542,7 +4684,7 @@
         <v>212</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
@@ -4573,14 +4715,14 @@
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -4608,7 +4750,7 @@
         <v>212</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
@@ -4637,14 +4779,14 @@
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
       <c r="K79" s="18" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L79" s="18"/>
       <c r="M79" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -4672,7 +4814,7 @@
         <v>213</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
@@ -4701,14 +4843,14 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="22">
         <v>81</v>
       </c>
@@ -4736,7 +4878,7 @@
         <v>213</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
@@ -4765,14 +4907,14 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>83</v>
       </c>
@@ -4800,7 +4942,7 @@
         <v>213</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
@@ -4829,14 +4971,14 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>85</v>
       </c>
@@ -4862,16 +5004,16 @@
         <v>213</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M86" s="8">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -4899,7 +5041,7 @@
         <v>217</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
@@ -4930,14 +5072,14 @@
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>88</v>
       </c>
@@ -4965,7 +5107,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -4996,7 +5138,7 @@
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
@@ -5027,7 +5169,7 @@
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L91" s="10" t="s">
         <v>302</v>
@@ -5036,7 +5178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>91</v>
       </c>
@@ -5064,7 +5206,7 @@
         <v>217</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
@@ -5095,14 +5237,14 @@
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>93</v>
       </c>
@@ -5130,7 +5272,7 @@
         <v>218</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
@@ -5161,14 +5303,14 @@
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>95</v>
       </c>
@@ -5179,7 +5321,7 @@
         <v>181</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6" t="s">
@@ -5196,7 +5338,7 @@
         <v>218</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
@@ -5227,14 +5369,14 @@
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>97</v>
       </c>
@@ -5262,7 +5404,7 @@
         <v>221</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
@@ -5293,14 +5435,14 @@
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>99</v>
       </c>
@@ -5328,14 +5470,14 @@
         <v>221</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>100</v>
       </c>
@@ -5363,7 +5505,7 @@
         <v>223</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
@@ -5394,14 +5536,14 @@
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>102</v>
       </c>
@@ -5429,7 +5571,7 @@
         <v>223</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
@@ -5460,14 +5602,14 @@
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>104</v>
       </c>
@@ -5495,7 +5637,7 @@
         <v>223</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
@@ -5526,14 +5668,14 @@
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>106</v>
       </c>
@@ -5561,7 +5703,7 @@
         <v>224</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
@@ -5592,14 +5734,14 @@
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>108</v>
       </c>
@@ -5627,14 +5769,14 @@
         <v>224</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>109</v>
       </c>
@@ -5662,14 +5804,14 @@
         <v>228</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>110</v>
       </c>
@@ -5697,14 +5839,14 @@
         <v>228</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>111</v>
       </c>
@@ -5732,14 +5874,14 @@
         <v>229</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>112</v>
       </c>
@@ -5767,14 +5909,14 @@
         <v>229</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>113</v>
       </c>
@@ -5800,14 +5942,14 @@
         <v>231</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>114</v>
       </c>
@@ -5833,14 +5975,14 @@
         <v>231</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>115</v>
       </c>
@@ -5868,14 +6010,14 @@
         <v>232</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -5901,14 +6043,14 @@
         <v>232</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>117</v>
       </c>
@@ -5934,14 +6076,14 @@
         <v>232</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>118</v>
       </c>
@@ -5969,14 +6111,14 @@
         <v>234</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>119</v>
       </c>
@@ -6004,14 +6146,14 @@
         <v>234</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>120</v>
       </c>
@@ -6039,14 +6181,14 @@
         <v>300</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>121</v>
       </c>
@@ -6074,14 +6216,14 @@
         <v>235</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>122</v>
       </c>
@@ -6109,14 +6251,14 @@
         <v>237</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>123</v>
       </c>
@@ -6144,14 +6286,14 @@
         <v>237</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>124</v>
       </c>
@@ -6179,14 +6321,14 @@
         <v>240</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>125</v>
       </c>
@@ -6214,7 +6356,7 @@
         <v>240</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
@@ -6226,13 +6368,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="C127" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="D127" s="9" t="s">
         <v>305</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>306</v>
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9" t="s">
@@ -6245,14 +6387,14 @@
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>127</v>
       </c>
@@ -6280,14 +6422,14 @@
         <v>242</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>128</v>
       </c>
@@ -6315,14 +6457,14 @@
         <v>242</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>129</v>
       </c>
@@ -6350,14 +6492,14 @@
         <v>243</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>130</v>
       </c>
@@ -6385,7 +6527,7 @@
         <v>243</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
@@ -6393,11 +6535,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M131" xr:uid="{B05D1357-A17E-4B05-B803-B367BB9C049C}">
-    <filterColumn colId="8">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M131" xr:uid="{B05D1357-A17E-4B05-B803-B367BB9C049C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6415,24 +6553,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>6</v>
@@ -6441,13 +6579,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>12</v>
@@ -6456,13 +6594,13 @@
         <v>196</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>16</v>
@@ -6471,13 +6609,13 @@
         <v>199</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>22</v>
@@ -6486,13 +6624,13 @@
         <v>200</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>202</v>
@@ -6501,13 +6639,13 @@
         <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>31</v>
@@ -6517,13 +6655,13 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>34</v>
@@ -6532,32 +6670,32 @@
         <v>205</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>36</v>
@@ -6566,13 +6704,13 @@
         <v>207</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>37</v>
@@ -6581,13 +6719,13 @@
         <v>208</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>38</v>
@@ -6596,13 +6734,13 @@
         <v>209</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>42</v>
@@ -6611,13 +6749,13 @@
         <v>212</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>43</v>
@@ -6626,13 +6764,13 @@
         <v>213</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>48</v>
@@ -6641,13 +6779,13 @@
         <v>217</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>49</v>
@@ -6656,13 +6794,13 @@
         <v>218</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>52</v>
@@ -6671,13 +6809,13 @@
         <v>221</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -6686,13 +6824,13 @@
         <v>223</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>55</v>
@@ -6701,13 +6839,13 @@
         <v>224</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>59</v>
@@ -6716,13 +6854,13 @@
         <v>228</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>60</v>
@@ -6731,13 +6869,13 @@
         <v>229</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>62</v>
@@ -6746,13 +6884,13 @@
         <v>231</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>63</v>
@@ -6761,13 +6899,13 @@
         <v>232</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>66</v>
@@ -6776,13 +6914,13 @@
         <v>234</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>68</v>
@@ -6791,15 +6929,15 @@
         <v>235</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>68</v>
@@ -6808,15 +6946,15 @@
         <v>300</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>70</v>
@@ -6825,13 +6963,13 @@
         <v>237</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>76</v>
@@ -6840,13 +6978,13 @@
         <v>240</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>78</v>
@@ -6855,13 +6993,13 @@
         <v>242</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>80</v>
@@ -6870,25 +7008,25 @@
         <v>243</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>108</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -6899,172 +7037,420 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A337F81-5FE2-493C-AFA8-0A38C4915F5A}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="61.5703125" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="D1" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="E1" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F3" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>543</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F5" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>513</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>534</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D8" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F8" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="E1" s="26" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="C9" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F9" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F11" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F12" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F13" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>505</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F14" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F15" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>386</v>
+      <c r="F16" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>519</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F17" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>522</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F18" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>523</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F19" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>525</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F20" s="7">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{1A337F81-5FE2-493C-AFA8-0A38C4915F5A}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E8">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:F20" xr:uid="{1A337F81-5FE2-493C-AFA8-0A38C4915F5A}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F20">
+      <sortCondition ref="F1:F20"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7085,19 +7471,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
         <v>341</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>342</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>343</v>
-      </c>
-      <c r="E1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7105,16 +7491,16 @@
         <v>68</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" t="s">
         <v>353</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>354</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>355</v>
-      </c>
-      <c r="E2" t="s">
-        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -7136,19 +7522,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" t="s">
         <v>348</v>
       </c>
-      <c r="B1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E1" t="s">
         <v>349</v>
-      </c>
-      <c r="D1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7156,16 +7542,16 @@
         <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7173,16 +7559,16 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D3" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="D3" t="s">
-        <v>396</v>
-      </c>
       <c r="E3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7190,16 +7576,16 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7207,16 +7593,16 @@
         <v>66</v>
       </c>
       <c r="B5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" t="s">
         <v>394</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="D5" t="s">
-        <v>396</v>
-      </c>
       <c r="E5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7224,16 +7610,16 @@
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF538CE6-4C0A-4392-A4E4-E3CA04D8A860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CEC64B-D87A-45E5-8F22-57654E008A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="559">
   <si>
     <t>Đời</t>
   </si>
@@ -789,9 +789,6 @@
     <t>Phiếu</t>
   </si>
   <si>
-    <t>Vẹt</t>
-  </si>
-  <si>
     <t>Lê Thị</t>
   </si>
   <si>
@@ -987,9 +984,6 @@
     <t>bà hai</t>
   </si>
   <si>
-    <t>vợ 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
@@ -1032,9 +1026,6 @@
     <t>Giỗ</t>
   </si>
   <si>
-    <t>17/11</t>
-  </si>
-  <si>
     <t>23/07</t>
   </si>
   <si>
@@ -1224,9 +1215,6 @@
     <t>image</t>
   </si>
   <si>
-    <t>chân dung</t>
-  </si>
-  <si>
     <t>chân dung 2</t>
   </si>
   <si>
@@ -1569,6 +1557,9 @@
     <t>Phúc Tuất</t>
   </si>
   <si>
+    <t>Phúc Cốc</t>
+  </si>
+  <si>
     <t>Phúc Tích</t>
   </si>
   <si>
@@ -1626,9 +1617,6 @@
     <t>Cụ Bà Đào, Pháp danh Diệu Hà,</t>
   </si>
   <si>
-    <t>cụ bà Quặm (vợ lẽ cụ Cốc) Giỗ 17/11 âm lịch</t>
-  </si>
-  <si>
     <t>Nguyễn Phúc Lan, Tự Thuần Tuệ  (chết trẻ )</t>
   </si>
   <si>
@@ -1659,9 +1647,6 @@
     <t>tên Tự : Thuần Bản ( theo ds cúng giỗ) ?</t>
   </si>
   <si>
-    <t>Vũ Thị Vạc, hiệu Diệu Đài giỗ 02/02 ?</t>
-  </si>
-  <si>
     <t>15/10</t>
   </si>
   <si>
@@ -1671,13 +1656,70 @@
     <t>ThuTuHienThi</t>
   </si>
   <si>
-    <t>Giỗ 12/11</t>
-  </si>
-  <si>
-    <t>12/11</t>
-  </si>
-  <si>
-    <t>Nguyễn Quý Công Tự Phúc Cốc</t>
+    <t>Mất ngày 11/12/1954 tức 17/11 ÂL</t>
+  </si>
+  <si>
+    <t>cụ bà Quặm (vợ lẽ cụ Cốc)  Mất ngày 11/12/1954 tức 17/11 Âm lịch</t>
+  </si>
+  <si>
+    <t>17/11/1954</t>
+  </si>
+  <si>
+    <t>12/11/1977</t>
+  </si>
+  <si>
+    <t>Nguyễn Quý Công Tự Phúc Cốc. Chết 12/11/1977 Đinh Tỵ , thọ 73 tuổi</t>
+  </si>
+  <si>
+    <t>Giỗ 12/11 Đinh Tỵ</t>
+  </si>
+  <si>
+    <t>Vũ Thị Vạc, hiệu Diệu Đạt giỗ 02/02 ?</t>
+  </si>
+  <si>
+    <t>Vũ Quý Thị</t>
+  </si>
+  <si>
+    <t>Vịt</t>
+  </si>
+  <si>
+    <t>02/02</t>
+  </si>
+  <si>
+    <t>Vũ Quý Thị Vịt, hiệu Diệu Đạt, mất 02/02</t>
+  </si>
+  <si>
+    <t>Giỗ 13/08</t>
+  </si>
+  <si>
+    <t>images/3ba.jpg</t>
+  </si>
+  <si>
+    <t>images/Backdrop2026.jpg</t>
+  </si>
+  <si>
+    <t>images/CacBa.jpg</t>
+  </si>
+  <si>
+    <t>Ảnh tập thể</t>
+  </si>
+  <si>
+    <t>Background 2026</t>
+  </si>
+  <si>
+    <t>images/ChiVinhAn.jpg</t>
+  </si>
+  <si>
+    <t>images/XuanHien.jpg</t>
+  </si>
+  <si>
+    <t>Ảnh gia đình</t>
+  </si>
+  <si>
+    <t>images/BatTay.jpg</t>
+  </si>
+  <si>
+    <t>Bắt tay giữa Xuân Đông và Xuân Trường</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1894,6 +1936,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2232,7 +2276,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
@@ -2262,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>119</v>
@@ -2436,7 +2480,7 @@
         <v>121</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>11</v>
@@ -2447,7 +2491,7 @@
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="M7" s="17">
         <v>5</v>
@@ -2482,7 +2526,7 @@
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="M8" s="2">
         <v>5</v>
@@ -2496,10 +2540,10 @@
         <v>199</v>
       </c>
       <c r="C9" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>298</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>299</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="17" t="s">
@@ -2544,7 +2588,7 @@
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M10" s="2">
         <v>5</v>
@@ -2579,7 +2623,7 @@
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M11" s="2">
         <v>5</v>
@@ -2614,7 +2658,7 @@
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="M12" s="2">
         <v>5</v>
@@ -2634,7 +2678,7 @@
         <v>245</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>11</v>
@@ -2678,7 +2722,7 @@
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M14" s="2">
         <v>6</v>
@@ -2713,7 +2757,7 @@
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M15" s="2">
         <v>6</v>
@@ -2746,7 +2790,7 @@
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M16" s="2">
         <v>6</v>
@@ -2818,10 +2862,10 @@
         <v>202</v>
       </c>
       <c r="C19" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>298</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>299</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="17" t="s">
@@ -2851,7 +2895,7 @@
         <v>124</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>8</v>
@@ -2865,7 +2909,9 @@
         <v>200</v>
       </c>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>548</v>
+      </c>
       <c r="M20" s="2">
         <v>6</v>
       </c>
@@ -2878,10 +2924,10 @@
         <v>203</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>175</v>
+        <v>544</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>248</v>
+        <v>545</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="17" t="s">
@@ -2893,7 +2939,7 @@
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M21" s="17">
         <v>6</v>
@@ -2910,7 +2956,7 @@
         <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
@@ -2939,7 +2985,7 @@
         <v>204</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>77</v>
@@ -3002,12 +3048,18 @@
       <c r="D25" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>504</v>
+      </c>
       <c r="F25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
+      <c r="G25" s="2">
+        <v>1904</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1977</v>
+      </c>
       <c r="I25" s="2" t="s">
         <v>31</v>
       </c>
@@ -3034,7 +3086,7 @@
         <v>175</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="17" t="s">
@@ -3046,7 +3098,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="M26" s="17">
         <v>7</v>
@@ -3057,25 +3109,29 @@
         <v>26</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>175</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="18"/>
+      <c r="G27" s="14">
+        <v>1912</v>
+      </c>
+      <c r="H27" s="18">
+        <v>1954</v>
+      </c>
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18" t="s">
-        <v>314</v>
+        <v>537</v>
       </c>
       <c r="M27" s="17">
         <v>7</v>
@@ -3108,7 +3164,7 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
@@ -3123,10 +3179,10 @@
         <v>206</v>
       </c>
       <c r="C29" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>251</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>252</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="17" t="s">
@@ -3156,7 +3212,7 @@
         <v>128</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>8</v>
@@ -3174,7 +3230,7 @@
         <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
@@ -3192,7 +3248,7 @@
         <v>175</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="17" t="s">
@@ -3207,7 +3263,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="L31" s="18"/>
       <c r="M31" s="17">
@@ -3228,7 +3284,7 @@
         <v>129</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -3244,7 +3300,7 @@
         <v>205</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
@@ -3259,10 +3315,10 @@
         <v>208</v>
       </c>
       <c r="C33" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="D33" s="18" t="s">
         <v>254</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>255</v>
       </c>
       <c r="E33" s="16"/>
       <c r="F33" s="17" t="s">
@@ -3273,7 +3329,7 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="17">
@@ -3294,7 +3350,7 @@
         <v>130</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>8</v>
@@ -3310,7 +3366,7 @@
         <v>205</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
@@ -3325,7 +3381,7 @@
         <v>209</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D35" s="18" t="s">
         <v>130</v>
@@ -3341,7 +3397,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="L35" s="18"/>
       <c r="M35" s="17">
@@ -3362,13 +3418,13 @@
         <v>131</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
@@ -3378,10 +3434,10 @@
         <v>205</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="M36" s="3">
         <v>8</v>
@@ -3395,10 +3451,10 @@
         <v>210</v>
       </c>
       <c r="C37" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="D37" s="18" t="s">
         <v>298</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>299</v>
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="17" t="s">
@@ -3409,7 +3465,7 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L37" s="18"/>
       <c r="M37" s="17">
@@ -3442,10 +3498,10 @@
         <v>205</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M38" s="3">
         <v>8</v>
@@ -3459,10 +3515,10 @@
         <v>211</v>
       </c>
       <c r="C39" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39" s="18" t="s">
         <v>257</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>258</v>
       </c>
       <c r="E39" s="16"/>
       <c r="F39" s="17" t="s">
@@ -3473,7 +3529,7 @@
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="L39" s="18"/>
       <c r="M39" s="17">
@@ -3506,7 +3562,7 @@
         <v>205</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
@@ -3543,10 +3599,10 @@
         <v>205</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="M41" s="3">
         <v>8</v>
@@ -3560,10 +3616,10 @@
         <v>212</v>
       </c>
       <c r="C42" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D42" s="18" t="s">
         <v>259</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>260</v>
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="17" t="s">
@@ -3576,7 +3632,7 @@
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
@@ -3608,10 +3664,10 @@
         <v>34</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
@@ -3629,7 +3685,7 @@
         <v>175</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E44" s="16"/>
       <c r="F44" s="17" t="s">
@@ -3640,7 +3696,7 @@
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L44" s="18"/>
       <c r="M44" s="17">
@@ -3670,13 +3726,13 @@
         <v>34</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M45" s="3">
         <v>8</v>
@@ -3690,10 +3746,10 @@
         <v>214</v>
       </c>
       <c r="C46" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="D46" s="18" t="s">
         <v>262</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>263</v>
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="17" t="s">
@@ -3704,7 +3760,7 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
@@ -3734,13 +3790,13 @@
         <v>34</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M47" s="3">
         <v>8</v>
@@ -3754,10 +3810,10 @@
         <v>215</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="17" t="s">
@@ -3768,7 +3824,7 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
@@ -3803,7 +3859,7 @@
         <v>207</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
@@ -3838,7 +3894,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
@@ -3853,10 +3909,10 @@
         <v>216</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E51" s="21"/>
       <c r="F51" s="17" t="s">
@@ -3867,7 +3923,7 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
       <c r="K51" s="18" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
@@ -3904,7 +3960,7 @@
         <v>207</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
@@ -3922,7 +3978,7 @@
         <v>175</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E53" s="21"/>
       <c r="F53" s="17" t="s">
@@ -3935,7 +3991,7 @@
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
@@ -3972,7 +4028,7 @@
         <v>207</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
@@ -3990,7 +4046,7 @@
         <v>175</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E55" s="21"/>
       <c r="F55" s="17" t="s">
@@ -4003,7 +4059,7 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
@@ -4038,7 +4094,7 @@
         <v>207</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
@@ -4053,10 +4109,10 @@
         <v>219</v>
       </c>
       <c r="C57" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D57" s="18" t="s">
         <v>268</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>269</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="17" t="s">
@@ -4067,7 +4123,7 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="K57" s="18" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
@@ -4102,7 +4158,7 @@
         <v>207</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
@@ -4117,10 +4173,10 @@
         <v>220</v>
       </c>
       <c r="C59" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>270</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>271</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="17" t="s">
@@ -4133,7 +4189,7 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
@@ -4168,7 +4224,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
@@ -4183,10 +4239,10 @@
         <v>221</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="17" t="s">
@@ -4199,7 +4255,7 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
@@ -4234,7 +4290,7 @@
         <v>207</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
@@ -4249,7 +4305,7 @@
         <v>222</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>168</v>
@@ -4263,7 +4319,7 @@
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
       <c r="K63" s="18" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
@@ -4298,7 +4354,7 @@
         <v>208</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
@@ -4316,7 +4372,7 @@
         <v>175</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="17" t="s">
@@ -4327,7 +4383,7 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
@@ -4362,7 +4418,7 @@
         <v>208</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
@@ -4391,7 +4447,7 @@
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
       <c r="K67" s="18" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
@@ -4426,7 +4482,7 @@
         <v>208</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
@@ -4441,10 +4497,10 @@
         <v>225</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="17" t="s">
@@ -4455,7 +4511,7 @@
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
@@ -4490,7 +4546,7 @@
         <v>208</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
@@ -4505,10 +4561,10 @@
         <v>226</v>
       </c>
       <c r="C71" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="D71" s="18" t="s">
         <v>275</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>276</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="17" t="s">
@@ -4519,7 +4575,7 @@
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
@@ -4554,7 +4610,7 @@
         <v>208</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
@@ -4569,7 +4625,7 @@
         <v>227</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D73" s="18" t="s">
         <v>244</v>
@@ -4583,7 +4639,7 @@
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
@@ -4618,7 +4674,7 @@
         <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
@@ -4633,7 +4689,7 @@
         <v>228</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D75" s="18" t="s">
         <v>148</v>
@@ -4649,7 +4705,7 @@
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
       <c r="K75" s="18" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
@@ -4684,7 +4740,7 @@
         <v>212</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
@@ -4699,10 +4755,10 @@
         <v>229</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="17" t="s">
@@ -4715,7 +4771,7 @@
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
@@ -4750,7 +4806,7 @@
         <v>212</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
@@ -4765,10 +4821,10 @@
         <v>230</v>
       </c>
       <c r="C79" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="D79" s="18" t="s">
         <v>298</v>
-      </c>
-      <c r="D79" s="18" t="s">
-        <v>299</v>
       </c>
       <c r="E79" s="21"/>
       <c r="F79" s="17" t="s">
@@ -4779,7 +4835,7 @@
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
       <c r="K79" s="18" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L79" s="18"/>
       <c r="M79" s="17">
@@ -4814,7 +4870,7 @@
         <v>213</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
@@ -4832,7 +4888,7 @@
         <v>175</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E81" s="21"/>
       <c r="F81" s="17" t="s">
@@ -4843,7 +4899,7 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
@@ -4878,7 +4934,7 @@
         <v>213</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
@@ -4893,10 +4949,10 @@
         <v>232</v>
       </c>
       <c r="C83" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D83" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="9" t="s">
@@ -4907,7 +4963,7 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
@@ -4942,7 +4998,7 @@
         <v>213</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
@@ -4957,10 +5013,10 @@
         <v>233</v>
       </c>
       <c r="C85" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D85" s="10" t="s">
         <v>281</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>282</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="9" t="s">
@@ -4971,7 +5027,7 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
@@ -5004,10 +5060,10 @@
         <v>213</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M86" s="8">
         <v>9</v>
@@ -5041,7 +5097,7 @@
         <v>217</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
@@ -5072,7 +5128,7 @@
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
@@ -5107,7 +5163,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -5122,10 +5178,10 @@
         <v>235</v>
       </c>
       <c r="C90" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D90" s="10" t="s">
         <v>283</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="E90" s="13"/>
       <c r="F90" s="9" t="s">
@@ -5138,7 +5194,7 @@
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
@@ -5150,10 +5206,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>300</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>152</v>
@@ -5169,10 +5225,10 @@
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
       <c r="K91" s="10" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="L91" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M91" s="9">
         <v>10</v>
@@ -5206,7 +5262,7 @@
         <v>217</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
@@ -5221,10 +5277,10 @@
         <v>236</v>
       </c>
       <c r="C93" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>286</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9" t="s">
@@ -5237,7 +5293,7 @@
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
@@ -5272,7 +5328,7 @@
         <v>218</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
@@ -5287,10 +5343,10 @@
         <v>237</v>
       </c>
       <c r="C95" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D95" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9" t="s">
@@ -5303,7 +5359,7 @@
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
@@ -5321,7 +5377,7 @@
         <v>181</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6" t="s">
@@ -5338,7 +5394,7 @@
         <v>218</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
@@ -5353,7 +5409,7 @@
         <v>238</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>165</v>
@@ -5369,7 +5425,7 @@
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
@@ -5404,7 +5460,7 @@
         <v>221</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
@@ -5419,10 +5475,10 @@
         <v>239</v>
       </c>
       <c r="C99" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>291</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9" t="s">
@@ -5435,7 +5491,7 @@
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
@@ -5470,7 +5526,7 @@
         <v>221</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
@@ -5505,7 +5561,7 @@
         <v>223</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
@@ -5520,10 +5576,10 @@
         <v>240</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D102" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9" t="s">
@@ -5536,7 +5592,7 @@
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
@@ -5571,7 +5627,7 @@
         <v>223</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
@@ -5589,7 +5645,7 @@
         <v>186</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9" t="s">
@@ -5602,7 +5658,7 @@
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
@@ -5637,7 +5693,7 @@
         <v>223</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
@@ -5652,10 +5708,10 @@
         <v>241</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D106" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>295</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9" t="s">
@@ -5668,7 +5724,7 @@
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
@@ -5703,7 +5759,7 @@
         <v>224</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
@@ -5718,7 +5774,7 @@
         <v>243</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>158</v>
@@ -5734,7 +5790,7 @@
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
@@ -5769,7 +5825,7 @@
         <v>224</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
@@ -5804,7 +5860,7 @@
         <v>228</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
@@ -5839,7 +5895,7 @@
         <v>228</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
@@ -5874,7 +5930,7 @@
         <v>229</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
@@ -5909,7 +5965,7 @@
         <v>229</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
@@ -5942,7 +5998,7 @@
         <v>231</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
@@ -5975,7 +6031,7 @@
         <v>231</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
@@ -6010,7 +6066,7 @@
         <v>232</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
@@ -6043,7 +6099,7 @@
         <v>232</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
@@ -6076,7 +6132,7 @@
         <v>232</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
@@ -6111,7 +6167,7 @@
         <v>234</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
@@ -6146,7 +6202,7 @@
         <v>234</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
@@ -6178,10 +6234,10 @@
         <v>68</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
@@ -6216,7 +6272,7 @@
         <v>235</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
@@ -6251,7 +6307,7 @@
         <v>237</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
@@ -6286,7 +6342,7 @@
         <v>237</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
@@ -6321,7 +6377,7 @@
         <v>240</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
@@ -6356,7 +6412,7 @@
         <v>240</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
@@ -6368,13 +6424,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C127" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="D127" s="9" t="s">
         <v>304</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>305</v>
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9" t="s">
@@ -6387,7 +6443,7 @@
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="13" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
@@ -6422,7 +6478,7 @@
         <v>242</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
@@ -6457,7 +6513,7 @@
         <v>242</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
@@ -6492,7 +6548,7 @@
         <v>243</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
@@ -6527,7 +6583,7 @@
         <v>243</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
@@ -6553,24 +6609,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>322</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>6</v>
@@ -6579,13 +6635,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>12</v>
@@ -6594,13 +6650,13 @@
         <v>196</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>16</v>
@@ -6609,13 +6665,13 @@
         <v>199</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>22</v>
@@ -6624,13 +6680,13 @@
         <v>200</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>202</v>
@@ -6639,13 +6695,13 @@
         <v>29</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>31</v>
@@ -6655,13 +6711,13 @@
         <v>VA-6.05S1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>34</v>
@@ -6670,32 +6726,32 @@
         <v>205</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>336</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>36</v>
@@ -6704,13 +6760,13 @@
         <v>207</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>37</v>
@@ -6719,13 +6775,13 @@
         <v>208</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>38</v>
@@ -6734,13 +6790,13 @@
         <v>209</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>42</v>
@@ -6749,13 +6805,13 @@
         <v>212</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>43</v>
@@ -6764,13 +6820,13 @@
         <v>213</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>48</v>
@@ -6779,13 +6835,13 @@
         <v>217</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>49</v>
@@ -6794,13 +6850,13 @@
         <v>218</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>52</v>
@@ -6809,13 +6865,13 @@
         <v>221</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>54</v>
@@ -6824,13 +6880,13 @@
         <v>223</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>55</v>
@@ -6839,13 +6895,13 @@
         <v>224</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>59</v>
@@ -6854,13 +6910,13 @@
         <v>228</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>60</v>
@@ -6869,13 +6925,13 @@
         <v>229</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>62</v>
@@ -6884,13 +6940,13 @@
         <v>231</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>63</v>
@@ -6899,13 +6955,13 @@
         <v>232</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B24" s="24" t="s">
         <v>66</v>
@@ -6914,13 +6970,13 @@
         <v>234</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>68</v>
@@ -6929,32 +6985,32 @@
         <v>235</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>68</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B27" s="24" t="s">
         <v>70</v>
@@ -6963,13 +7019,13 @@
         <v>237</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B28" s="24" t="s">
         <v>76</v>
@@ -6978,13 +7034,13 @@
         <v>240</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>78</v>
@@ -6993,13 +7049,13 @@
         <v>242</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>80</v>
@@ -7008,25 +7064,25 @@
         <v>243</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>108</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -7037,7 +7093,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A337F81-5FE2-493C-AFA8-0A38C4915F5A}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -7048,403 +7104,423 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="E1" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C1" s="29" t="s">
-        <v>385</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>327</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>328</v>
+      <c r="B3" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>503</v>
+        <v>498</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>499</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F3" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>328</v>
+      <c r="B4" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>543</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>544</v>
+        <v>540</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>541</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F4" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>539</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>540</v>
+      <c r="B5" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>534</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>535</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F5" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>512</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>513</v>
+      <c r="B6" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>509</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>510</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F6" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>532</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>533</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>534</v>
+      <c r="B7" s="29" t="s">
+        <v>528</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>529</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>530</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F7" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="29" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F8" s="7">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="29" t="s">
         <v>207</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F9" s="7">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F10" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="29" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F11" s="7">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="29" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F12" s="7">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="29" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F13" s="7">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>506</v>
+      <c r="B14" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>502</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F14" s="7">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>516</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>528</v>
+      <c r="B15" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>524</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F15" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>311</v>
+      <c r="A16" s="29" t="s">
+        <v>310</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>329</v>
+        <v>539</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F16" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="27" t="s">
-        <v>328</v>
+      <c r="B17" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>518</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>519</v>
+        <v>515</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>516</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F17" s="7">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>521</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>522</v>
+      <c r="B18" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>519</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F18" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="D19" s="29" t="s">
         <v>523</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>526</v>
-      </c>
       <c r="E19" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F19" s="7">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="B20" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>524</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>525</v>
+      <c r="B20" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>522</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F20" s="7">
         <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="F21" s="27">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -7471,19 +7547,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E1" t="s">
         <v>340</v>
-      </c>
-      <c r="C1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7491,16 +7567,16 @@
         <v>68</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="C2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E2" t="s">
         <v>352</v>
-      </c>
-      <c r="C2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E2" t="s">
-        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -7510,7 +7586,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2870D094-0F04-43A9-85F0-3281621B51DF}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -7522,19 +7598,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7542,16 +7618,16 @@
         <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>455</v>
+        <v>550</v>
       </c>
       <c r="D2" t="s">
-        <v>393</v>
+        <v>553</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7559,33 +7635,33 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>453</v>
+        <v>549</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>552</v>
       </c>
       <c r="E4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7593,16 +7669,16 @@
         <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7610,16 +7686,84 @@
         <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E6" t="s">
-        <v>350</v>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="D8" t="s">
+        <v>552</v>
+      </c>
+      <c r="E8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="D9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="D10" t="s">
+        <v>556</v>
+      </c>
+      <c r="E10" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CEC64B-D87A-45E5-8F22-57654E008A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2FA415-BBA5-4729-9005-DBC981CC408A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="559">
   <si>
     <t>Đời</t>
   </si>
@@ -1248,12 +1248,6 @@
     <t>images/persons/VA-8.05.jpg</t>
   </si>
   <si>
-    <t>images/persons/VA-8.05S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.06.jpg</t>
-  </si>
-  <si>
     <t>images/persons/VA-8.07.jpg</t>
   </si>
   <si>
@@ -1263,9 +1257,6 @@
     <t>images/persons/VA-8.08.jpg</t>
   </si>
   <si>
-    <t>images/persons/VA-8.08S1.jpg</t>
-  </si>
-  <si>
     <t>images/persons/VA-8.09.jpg</t>
   </si>
   <si>
@@ -1368,9 +1359,6 @@
     <t>images/persons/VA-9.16.jpg</t>
   </si>
   <si>
-    <t>images/persons/VA-9.16S1.jpg</t>
-  </si>
-  <si>
     <t>images/persons/VA-9.17.jpg</t>
   </si>
   <si>
@@ -1389,9 +1377,6 @@
     <t>images/persons/VA-9.19S1.jpg</t>
   </si>
   <si>
-    <t>images/persons/VA-9.20.jpg</t>
-  </si>
-  <si>
     <t>images/persons/VA-10.01.jpg</t>
   </si>
   <si>
@@ -1404,9 +1389,6 @@
     <t>images/persons/VA-10.02S1.jpg</t>
   </si>
   <si>
-    <t>images/persons/VA-10.02S2.jpg</t>
-  </si>
-  <si>
     <t>images/persons/VA-10.03.jpg</t>
   </si>
   <si>
@@ -1720,6 +1702,24 @@
   </si>
   <si>
     <t>Bắt tay giữa Xuân Đông và Xuân Trường</t>
+  </si>
+  <si>
+    <t>Trần</t>
+  </si>
+  <si>
+    <t>Chanh</t>
+  </si>
+  <si>
+    <t>images/ConTraiVA.jpg</t>
+  </si>
+  <si>
+    <t>images/MoToVA.jpg</t>
+  </si>
+  <si>
+    <t>Ảnh Mộ Tổ Phúc Bằng</t>
+  </si>
+  <si>
+    <t>Tập thể Nam</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +1908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1936,12 +1936,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2335,7 +2333,9 @@
         <v>8</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2">
+        <v>1900</v>
+      </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -2364,7 +2364,9 @@
         <v>11</v>
       </c>
       <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="H3" s="19">
+        <v>1900</v>
+      </c>
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
@@ -2393,7 +2395,9 @@
         <v>8</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2">
+        <v>1900</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>6</v>
       </c>
@@ -2424,7 +2428,9 @@
         <v>11</v>
       </c>
       <c r="G5" s="19"/>
-      <c r="H5" s="18"/>
+      <c r="H5" s="18">
+        <v>1900</v>
+      </c>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -2453,7 +2459,9 @@
         <v>8</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2">
+        <v>1900</v>
+      </c>
       <c r="I6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2486,12 +2494,14 @@
         <v>11</v>
       </c>
       <c r="G7" s="19"/>
-      <c r="H7" s="18"/>
+      <c r="H7" s="18">
+        <v>1900</v>
+      </c>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="M7" s="17">
         <v>5</v>
@@ -2517,7 +2527,9 @@
         <v>8</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2">
+        <v>1900</v>
+      </c>
       <c r="I8" s="2" t="s">
         <v>6</v>
       </c>
@@ -2526,7 +2538,7 @@
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="M8" s="2">
         <v>5</v>
@@ -2550,7 +2562,9 @@
         <v>11</v>
       </c>
       <c r="G9" s="19"/>
-      <c r="H9" s="18"/>
+      <c r="H9" s="18">
+        <v>1900</v>
+      </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
@@ -2579,7 +2593,9 @@
         <v>8</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>1900</v>
+      </c>
       <c r="I10" s="2" t="s">
         <v>6</v>
       </c>
@@ -2614,7 +2630,9 @@
         <v>8</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2">
+        <v>1900</v>
+      </c>
       <c r="I11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2649,7 +2667,9 @@
         <v>8</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>1900</v>
+      </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
       </c>
@@ -2658,7 +2678,7 @@
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="M12" s="2">
         <v>5</v>
@@ -2684,7 +2704,9 @@
         <v>11</v>
       </c>
       <c r="G13" s="19"/>
-      <c r="H13" s="18"/>
+      <c r="H13" s="18">
+        <v>1900</v>
+      </c>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
@@ -2713,7 +2735,9 @@
         <v>8</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2">
+        <v>1900</v>
+      </c>
       <c r="I14" s="2" t="s">
         <v>12</v>
       </c>
@@ -2748,7 +2772,9 @@
         <v>8</v>
       </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2">
+        <v>1900</v>
+      </c>
       <c r="I15" s="2" t="s">
         <v>12</v>
       </c>
@@ -2781,7 +2807,9 @@
         <v>11</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2">
+        <v>1900</v>
+      </c>
       <c r="I16" s="2" t="s">
         <v>12</v>
       </c>
@@ -2814,7 +2842,9 @@
         <v>8</v>
       </c>
       <c r="G17" s="19"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="18">
+        <v>1900</v>
+      </c>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
@@ -2841,7 +2871,9 @@
         <v>11</v>
       </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2">
+        <v>1900</v>
+      </c>
       <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
@@ -2872,7 +2904,9 @@
         <v>8</v>
       </c>
       <c r="G19" s="19"/>
-      <c r="H19" s="18"/>
+      <c r="H19" s="18">
+        <v>1900</v>
+      </c>
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
       <c r="K19" s="18"/>
@@ -2895,13 +2929,15 @@
         <v>124</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2">
+        <v>1900</v>
+      </c>
       <c r="I20" s="2" t="s">
         <v>22</v>
       </c>
@@ -2910,7 +2946,7 @@
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="M20" s="2">
         <v>6</v>
@@ -2924,22 +2960,24 @@
         <v>203</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="19"/>
-      <c r="H21" s="18"/>
+      <c r="H21" s="18">
+        <v>1900</v>
+      </c>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="M21" s="17">
         <v>6</v>
@@ -2963,7 +3001,9 @@
         <v>8</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2">
+        <v>1900</v>
+      </c>
       <c r="I22" s="2" t="s">
         <v>22</v>
       </c>
@@ -2995,7 +3035,9 @@
         <v>11</v>
       </c>
       <c r="G23" s="19"/>
-      <c r="H23" s="18"/>
+      <c r="H23" s="18">
+        <v>1900</v>
+      </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
@@ -3022,7 +3064,9 @@
         <v>11</v>
       </c>
       <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="H24" s="2">
+        <v>1900</v>
+      </c>
       <c r="I24" s="2" t="s">
         <v>202</v>
       </c>
@@ -3049,7 +3093,7 @@
         <v>126</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>8</v>
@@ -3069,7 +3113,7 @@
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="M25" s="2">
         <v>7</v>
@@ -3098,7 +3142,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="M26" s="17">
         <v>7</v>
@@ -3131,7 +3175,7 @@
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="M27" s="17">
         <v>7</v>
@@ -3212,7 +3256,7 @@
         <v>128</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>8</v>
@@ -3284,7 +3328,7 @@
         <v>129</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -3350,7 +3394,7 @@
         <v>130</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>8</v>
@@ -3418,7 +3462,7 @@
         <v>131</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
@@ -3437,7 +3481,7 @@
         <v>398</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="M36" s="3">
         <v>8</v>
@@ -3528,9 +3572,7 @@
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
-      <c r="K39" s="18" t="s">
-        <v>401</v>
-      </c>
+      <c r="K39" s="18"/>
       <c r="L39" s="18"/>
       <c r="M39" s="17">
         <v>8</v>
@@ -3561,9 +3603,7 @@
       <c r="J40" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>402</v>
-      </c>
+      <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3">
         <v>8</v>
@@ -3599,7 +3639,7 @@
         <v>205</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>391</v>
@@ -3632,7 +3672,7 @@
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
@@ -3667,7 +3707,7 @@
         <v>310</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
@@ -3695,9 +3735,7 @@
       <c r="H44" s="18"/>
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
-      <c r="K44" s="18" t="s">
-        <v>406</v>
-      </c>
+      <c r="K44" s="18"/>
       <c r="L44" s="18"/>
       <c r="M44" s="17">
         <v>8</v>
@@ -3729,7 +3767,7 @@
         <v>310</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>314</v>
@@ -3760,7 +3798,7 @@
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
@@ -3793,7 +3831,7 @@
         <v>310</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>315</v>
@@ -3824,7 +3862,7 @@
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
@@ -3859,7 +3897,7 @@
         <v>207</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
@@ -3894,7 +3932,7 @@
         <v>207</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
@@ -3923,7 +3961,7 @@
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
       <c r="K51" s="18" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
@@ -3960,7 +3998,7 @@
         <v>207</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
@@ -3991,7 +4029,7 @@
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
       <c r="K53" s="18" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
@@ -4028,7 +4066,7 @@
         <v>207</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
@@ -4059,7 +4097,7 @@
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
       <c r="K55" s="18" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
@@ -4094,7 +4132,7 @@
         <v>207</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
@@ -4123,7 +4161,7 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="K57" s="18" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
@@ -4158,7 +4196,7 @@
         <v>207</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
@@ -4189,7 +4227,7 @@
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
       <c r="K59" s="18" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
@@ -4224,7 +4262,7 @@
         <v>207</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
@@ -4255,7 +4293,7 @@
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
       <c r="K61" s="18" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
@@ -4290,7 +4328,7 @@
         <v>207</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
@@ -4319,7 +4357,7 @@
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
       <c r="K63" s="18" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
@@ -4354,7 +4392,7 @@
         <v>208</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
@@ -4383,7 +4421,7 @@
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
       <c r="K65" s="18" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
@@ -4418,7 +4456,7 @@
         <v>208</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
@@ -4447,7 +4485,7 @@
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
       <c r="K67" s="18" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
@@ -4482,7 +4520,7 @@
         <v>208</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
@@ -4511,7 +4549,7 @@
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
       <c r="K69" s="18" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
@@ -4546,7 +4584,7 @@
         <v>208</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
@@ -4575,7 +4613,7 @@
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
       <c r="K71" s="18" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
@@ -4610,7 +4648,7 @@
         <v>208</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
@@ -4639,7 +4677,7 @@
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
       <c r="K73" s="18" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
@@ -4674,7 +4712,7 @@
         <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
@@ -4705,7 +4743,7 @@
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
       <c r="K75" s="18" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
@@ -4740,7 +4778,7 @@
         <v>212</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
@@ -4771,7 +4809,7 @@
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
       <c r="K77" s="18" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
@@ -4806,7 +4844,7 @@
         <v>212</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
@@ -4821,10 +4859,10 @@
         <v>230</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>297</v>
+        <v>553</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>298</v>
+        <v>554</v>
       </c>
       <c r="E79" s="21"/>
       <c r="F79" s="17" t="s">
@@ -4834,9 +4872,7 @@
       <c r="H79" s="18"/>
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
-      <c r="K79" s="18" t="s">
-        <v>441</v>
-      </c>
+      <c r="K79" s="18"/>
       <c r="L79" s="18"/>
       <c r="M79" s="17">
         <v>9</v>
@@ -4870,7 +4906,7 @@
         <v>213</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
@@ -4899,7 +4935,7 @@
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
@@ -4934,7 +4970,7 @@
         <v>213</v>
       </c>
       <c r="K82" s="22" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
@@ -4963,7 +4999,7 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
@@ -4998,7 +5034,7 @@
         <v>213</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
@@ -5027,7 +5063,7 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" s="10" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
@@ -5059,9 +5095,7 @@
       <c r="J86" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="K86" s="8" t="s">
-        <v>448</v>
-      </c>
+      <c r="K86" s="8"/>
       <c r="L86" s="8" t="s">
         <v>306</v>
       </c>
@@ -5097,7 +5131,7 @@
         <v>217</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
@@ -5128,7 +5162,7 @@
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
       <c r="K88" s="10" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
@@ -5163,7 +5197,7 @@
         <v>217</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -5194,7 +5228,7 @@
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
       <c r="K90" s="10" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
@@ -5224,9 +5258,7 @@
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
       <c r="J91" s="10"/>
-      <c r="K91" s="10" t="s">
-        <v>453</v>
-      </c>
+      <c r="K91" s="10"/>
       <c r="L91" s="10" t="s">
         <v>301</v>
       </c>
@@ -5262,7 +5294,7 @@
         <v>217</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
@@ -5293,7 +5325,7 @@
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
@@ -5328,7 +5360,7 @@
         <v>218</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
@@ -5359,7 +5391,7 @@
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
       <c r="K95" s="10" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
@@ -5394,7 +5426,7 @@
         <v>218</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
@@ -5425,7 +5457,7 @@
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
@@ -5460,7 +5492,7 @@
         <v>221</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
@@ -5491,7 +5523,7 @@
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
@@ -5526,7 +5558,7 @@
         <v>221</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
@@ -5561,7 +5593,7 @@
         <v>223</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
@@ -5592,7 +5624,7 @@
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
       <c r="K102" s="10" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
@@ -5627,7 +5659,7 @@
         <v>223</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
@@ -5642,23 +5674,23 @@
         <v>242</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>186</v>
+        <v>293</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G104" s="9">
-        <v>1983</v>
+        <v>1972</v>
       </c>
       <c r="H104" s="10"/>
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
       <c r="K104" s="10" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
@@ -5693,7 +5725,7 @@
         <v>223</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
@@ -5708,23 +5740,23 @@
         <v>241</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>293</v>
+        <v>186</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G106" s="9">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="H106" s="10"/>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
       <c r="K106" s="10" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
@@ -5759,7 +5791,7 @@
         <v>224</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
@@ -5790,7 +5822,7 @@
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
@@ -5825,7 +5857,7 @@
         <v>224</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
@@ -5860,7 +5892,7 @@
         <v>228</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
@@ -5895,7 +5927,7 @@
         <v>228</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
@@ -5930,7 +5962,7 @@
         <v>229</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
@@ -5965,7 +5997,7 @@
         <v>229</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
@@ -5998,7 +6030,7 @@
         <v>231</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
@@ -6031,7 +6063,7 @@
         <v>231</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
@@ -6066,7 +6098,7 @@
         <v>232</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
@@ -6099,7 +6131,7 @@
         <v>232</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
@@ -6132,7 +6164,7 @@
         <v>232</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
@@ -6167,7 +6199,7 @@
         <v>234</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
@@ -6202,7 +6234,7 @@
         <v>234</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
@@ -6237,7 +6269,7 @@
         <v>299</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
@@ -6272,7 +6304,7 @@
         <v>235</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
@@ -6307,7 +6339,7 @@
         <v>237</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
@@ -6342,7 +6374,7 @@
         <v>237</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
@@ -6377,7 +6409,7 @@
         <v>240</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
@@ -6412,7 +6444,7 @@
         <v>240</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
@@ -6443,7 +6475,7 @@
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
       <c r="K127" s="13" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
@@ -6478,7 +6510,7 @@
         <v>242</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
@@ -6513,7 +6545,7 @@
         <v>242</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
@@ -6548,7 +6580,7 @@
         <v>243</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
@@ -6583,7 +6615,7 @@
         <v>243</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
@@ -7104,27 +7136,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>325</v>
       </c>
       <c r="E1" s="25" t="s">
         <v>380</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -7134,7 +7166,7 @@
         <v>379</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>381</v>
@@ -7144,17 +7176,17 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="7" t="s">
         <v>326</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>499</v>
+        <v>492</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>493</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>381</v>
@@ -7164,17 +7196,17 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="7" t="s">
         <v>326</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>540</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>541</v>
+        <v>534</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>535</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>381</v>
@@ -7184,17 +7216,17 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C5" s="29" t="s">
-        <v>534</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>535</v>
+      <c r="C5" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>529</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>381</v>
@@ -7204,17 +7236,17 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>509</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>510</v>
+      <c r="C6" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>504</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>381</v>
@@ -7224,17 +7256,17 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>528</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>529</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>530</v>
+      <c r="B7" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>524</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>381</v>
@@ -7244,7 +7276,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -7254,7 +7286,7 @@
         <v>384</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>381</v>
@@ -7264,7 +7296,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="7" t="s">
         <v>207</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -7274,7 +7306,7 @@
         <v>383</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>381</v>
@@ -7284,8 +7316,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>47</v>
+      <c r="A10" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>326</v>
@@ -7294,7 +7326,7 @@
         <v>385</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>381</v>
@@ -7304,7 +7336,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="7" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -7314,7 +7346,7 @@
         <v>386</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>381</v>
@@ -7324,7 +7356,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -7334,7 +7366,7 @@
         <v>327</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>381</v>
@@ -7344,17 +7376,17 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>326</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>381</v>
@@ -7364,17 +7396,17 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="29" t="s">
-        <v>501</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>502</v>
+      <c r="C14" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>496</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>381</v>
@@ -7384,17 +7416,17 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>513</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>524</v>
+      <c r="C15" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>518</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>381</v>
@@ -7404,17 +7436,17 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="7" t="s">
         <v>310</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>326</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>381</v>
@@ -7424,17 +7456,17 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="7" t="s">
         <v>326</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>515</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>516</v>
+        <v>509</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>510</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>381</v>
@@ -7444,17 +7476,17 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>518</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>519</v>
+      <c r="C18" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>513</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>381</v>
@@ -7464,17 +7496,17 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C19" s="29" t="s">
-        <v>520</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>523</v>
+      <c r="C19" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>517</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>381</v>
@@ -7484,17 +7516,17 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C20" s="29" t="s">
-        <v>521</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>522</v>
+      <c r="C20" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>516</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>381</v>
@@ -7511,10 +7543,10 @@
         <v>326</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>381</v>
@@ -7586,7 +7618,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2870D094-0F04-43A9-85F0-3281621B51DF}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -7621,10 +7653,10 @@
         <v>389</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E2" t="s">
         <v>347</v>
@@ -7638,7 +7670,7 @@
         <v>389</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D3" t="s">
         <v>390</v>
@@ -7655,10 +7687,10 @@
         <v>389</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D4" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E4" t="s">
         <v>347</v>
@@ -7672,7 +7704,7 @@
         <v>389</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D5" t="s">
         <v>390</v>
@@ -7689,10 +7721,10 @@
         <v>389</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E6" t="s">
         <v>347</v>
@@ -7706,10 +7738,10 @@
         <v>389</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D7" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E7" t="s">
         <v>347</v>
@@ -7723,10 +7755,10 @@
         <v>389</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D8" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E8" t="s">
         <v>347</v>
@@ -7740,10 +7772,10 @@
         <v>389</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D9" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="E9" t="s">
         <v>347</v>
@@ -7757,12 +7789,46 @@
         <v>389</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="D10" t="s">
+        <v>550</v>
+      </c>
+      <c r="E10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>389</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
+        <v>558</v>
+      </c>
+      <c r="E11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D12" t="s">
+        <v>557</v>
+      </c>
+      <c r="E12" t="s">
         <v>347</v>
       </c>
     </row>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2FA415-BBA5-4729-9005-DBC981CC408A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31819BCC-73DF-44EC-A6C8-0EFAC02B7A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -6504,10 +6504,10 @@
       </c>
       <c r="H128" s="6"/>
       <c r="I128" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J128" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>484</v>
@@ -6539,10 +6539,10 @@
       </c>
       <c r="H129" s="6"/>
       <c r="I129" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K129" s="6" t="s">
         <v>485</v>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31819BCC-73DF-44EC-A6C8-0EFAC02B7A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A451CDA2-DEC7-4F4D-A7EA-7F0D62C69427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="567">
   <si>
     <t>Đời</t>
   </si>
@@ -1720,6 +1720,30 @@
   </si>
   <si>
     <t>Tập thể Nam</t>
+  </si>
+  <si>
+    <t>image/about/chi-vinh-an.jpg</t>
+  </si>
+  <si>
+    <t>Sơ đồ chi vĩnh an</t>
+  </si>
+  <si>
+    <t>images/about/so-do-nguyenxuan.jpg</t>
+  </si>
+  <si>
+    <t>images/about/ba-chi-nguyen-xuan.jpg</t>
+  </si>
+  <si>
+    <t>images/about/gia-pha-co.jpg</t>
+  </si>
+  <si>
+    <t>Sơ đổ Tổng Gia Phả họ Nguyễn Xuân từ đời 1</t>
+  </si>
+  <si>
+    <t>Hình thành ba nhánh Chi</t>
+  </si>
+  <si>
+    <t>Trang sách Gia phả Nguyễn Xuân</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +1932,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1940,6 +1964,9 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7618,7 +7645,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2870D094-0F04-43A9-85F0-3281621B51DF}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -7832,7 +7859,76 @@
         <v>347</v>
       </c>
     </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>559</v>
+      </c>
+      <c r="D13" t="s">
+        <v>560</v>
+      </c>
+      <c r="E13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>389</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>561</v>
+      </c>
+      <c r="D14" t="s">
+        <v>564</v>
+      </c>
+      <c r="E14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>389</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="D15" t="s">
+        <v>565</v>
+      </c>
+      <c r="E15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>389</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" t="s">
+        <v>566</v>
+      </c>
+      <c r="E16" t="s">
+        <v>347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A451CDA2-DEC7-4F4D-A7EA-7F0D62C69427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D003179-6120-4683-840A-043DD17A10CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
@@ -1722,9 +1722,6 @@
     <t>Tập thể Nam</t>
   </si>
   <si>
-    <t>image/about/chi-vinh-an.jpg</t>
-  </si>
-  <si>
     <t>Sơ đồ chi vĩnh an</t>
   </si>
   <si>
@@ -1744,6 +1741,9 @@
   </si>
   <si>
     <t>Trang sách Gia phả Nguyễn Xuân</t>
+  </si>
+  <si>
+    <t>images/about/chi-vinh-an.jpg</t>
   </si>
 </sst>
 </file>
@@ -7650,7 +7650,7 @@
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="57.42578125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -7867,10 +7867,10 @@
         <v>389</v>
       </c>
       <c r="C13" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="D13" t="s">
         <v>559</v>
-      </c>
-      <c r="D13" t="s">
-        <v>560</v>
       </c>
       <c r="E13" t="s">
         <v>347</v>
@@ -7884,10 +7884,10 @@
         <v>389</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D14" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E14" t="s">
         <v>347</v>
@@ -7901,10 +7901,10 @@
         <v>389</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E15" t="s">
         <v>347</v>
@@ -7918,13 +7918,13 @@
         <v>389</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D16" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E16" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/data/DATA_GIAPHA.xlsx
+++ b/data/DATA_GIAPHA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\giapha-template\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D003179-6120-4683-840A-043DD17A10CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAA4142-D835-4C0D-AB48-FBAD2FECA659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82229A43-EBB1-44A5-B6DE-F008EE3D4237}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONS" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="426">
   <si>
     <t>Đời</t>
   </si>
@@ -63,333 +63,81 @@
     <t>Mẹ</t>
   </si>
   <si>
-    <t>VA-4.02</t>
-  </si>
-  <si>
     <t>Phúc Bằng</t>
   </si>
   <si>
     <t>Nam</t>
   </si>
   <si>
-    <t>VA-4.02S1</t>
-  </si>
-  <si>
     <t>Từ Liễn</t>
   </si>
   <si>
     <t>Nữ</t>
   </si>
   <si>
-    <t>VA-5.01</t>
-  </si>
-  <si>
     <t>Xuân Dân</t>
   </si>
   <si>
-    <t>VA-5.02</t>
-  </si>
-  <si>
     <t>Xuân Khải</t>
   </si>
   <si>
-    <t>VA-5.03</t>
-  </si>
-  <si>
     <t>Xuân Bản</t>
   </si>
   <si>
-    <t>VA-5.04</t>
-  </si>
-  <si>
     <t>Xuân Cự</t>
   </si>
   <si>
-    <t>VA-5.05</t>
-  </si>
-  <si>
     <t>Xuân Tùng</t>
   </si>
   <si>
-    <t>VA-5.06</t>
-  </si>
-  <si>
     <t>Xuân Bang</t>
   </si>
   <si>
-    <t>VA-6.01</t>
-  </si>
-  <si>
     <t>Xuân Lộc</t>
   </si>
   <si>
-    <t>VA-6.02</t>
-  </si>
-  <si>
     <t>Xuân Đào</t>
   </si>
   <si>
-    <t>VA-6.03</t>
-  </si>
-  <si>
-    <t>VA-6.04</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Quý</t>
-  </si>
-  <si>
-    <t>VA-6.05</t>
-  </si>
-  <si>
-    <t>VA-6.06</t>
-  </si>
-  <si>
-    <t>VA-7.01</t>
-  </si>
-  <si>
-    <t>VA-7.02</t>
-  </si>
-  <si>
-    <t>VA-7.03</t>
-  </si>
-  <si>
-    <t>VA-8.01</t>
-  </si>
-  <si>
-    <t>VA-8.02</t>
-  </si>
-  <si>
-    <t>VA-8.03</t>
-  </si>
-  <si>
-    <t>VA-8.04</t>
-  </si>
-  <si>
-    <t>VA-8.05</t>
-  </si>
-  <si>
-    <t>VA-8.06</t>
-  </si>
-  <si>
-    <t>VA-8.07</t>
-  </si>
-  <si>
-    <t>VA-8.08</t>
-  </si>
-  <si>
-    <t>VA-8.09</t>
-  </si>
-  <si>
-    <t>VA-8.10</t>
-  </si>
-  <si>
-    <t>VA-9.01</t>
-  </si>
-  <si>
-    <t>VA-9.02</t>
-  </si>
-  <si>
-    <t>VA-9.03</t>
-  </si>
-  <si>
-    <t>VA-9.04</t>
-  </si>
-  <si>
-    <t>VA-9.05</t>
-  </si>
-  <si>
-    <t>VA-9.06</t>
-  </si>
-  <si>
-    <t>VA-9.07</t>
-  </si>
-  <si>
-    <t>VA-9.08</t>
-  </si>
-  <si>
-    <t>VA-9.09</t>
-  </si>
-  <si>
-    <t>VA-9.10</t>
-  </si>
-  <si>
-    <t>VA-9.11</t>
-  </si>
-  <si>
-    <t>VA-9.12</t>
-  </si>
-  <si>
-    <t>VA-9.13</t>
-  </si>
-  <si>
-    <t>VA-9.14</t>
-  </si>
-  <si>
-    <t>VA-9.15</t>
-  </si>
-  <si>
-    <t>VA-9.16</t>
-  </si>
-  <si>
-    <t>VA-9.17</t>
-  </si>
-  <si>
-    <t>VA-9.18</t>
-  </si>
-  <si>
-    <t>VA-9.19</t>
-  </si>
-  <si>
-    <t>VA-9.20</t>
-  </si>
-  <si>
-    <t>VA-10.01</t>
-  </si>
-  <si>
     <t>Bích</t>
   </si>
   <si>
-    <t>VA-10.02</t>
-  </si>
-  <si>
-    <t>VA-10.03</t>
-  </si>
-  <si>
-    <t>VA-10.04</t>
-  </si>
-  <si>
     <t>Độ</t>
   </si>
   <si>
-    <t>VA-10.05</t>
-  </si>
-  <si>
-    <t>VA-10.06</t>
-  </si>
-  <si>
     <t>Quý</t>
   </si>
   <si>
-    <t>VA-10.07</t>
-  </si>
-  <si>
-    <t>VA-10.08</t>
-  </si>
-  <si>
     <t>Tâm</t>
   </si>
   <si>
-    <t>VA-10.09</t>
-  </si>
-  <si>
-    <t>VA-10.10</t>
-  </si>
-  <si>
-    <t>VA-10.11</t>
-  </si>
-  <si>
     <t>Hùng</t>
   </si>
   <si>
-    <t>VA-10.12</t>
-  </si>
-  <si>
-    <t>VA-10.13</t>
-  </si>
-  <si>
     <t>Cường</t>
   </si>
   <si>
-    <t>VA-10.14</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Phúc</t>
-  </si>
-  <si>
-    <t>VA-10.15</t>
-  </si>
-  <si>
     <t>Đông</t>
   </si>
   <si>
-    <t>VA-10.16</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Minh</t>
-  </si>
-  <si>
-    <t>VA-10.17</t>
-  </si>
-  <si>
     <t>Tiến</t>
   </si>
   <si>
-    <t>VA-10.18</t>
-  </si>
-  <si>
-    <t>VA-10.19</t>
-  </si>
-  <si>
     <t>Trường</t>
   </si>
   <si>
-    <t>VA-10.20</t>
-  </si>
-  <si>
-    <t>VA-10.21</t>
-  </si>
-  <si>
-    <t>VA-11.01</t>
-  </si>
-  <si>
-    <t>VA-11.02</t>
-  </si>
-  <si>
-    <t>VA-11.03</t>
-  </si>
-  <si>
-    <t>Thanh</t>
-  </si>
-  <si>
-    <t>VA-11.04</t>
-  </si>
-  <si>
-    <t>VA-11.05</t>
-  </si>
-  <si>
     <t>Sơn</t>
   </si>
   <si>
-    <t>VA-11.06</t>
-  </si>
-  <si>
-    <t>VA-11.07</t>
-  </si>
-  <si>
     <t>Tùng</t>
   </si>
   <si>
-    <t>VA-11.08</t>
-  </si>
-  <si>
-    <t>VA-11.09</t>
-  </si>
-  <si>
     <t>Hưng</t>
   </si>
   <si>
-    <t>VA-11.10</t>
-  </si>
-  <si>
-    <t>VA-11.11</t>
-  </si>
-  <si>
     <t>Hiếu</t>
   </si>
   <si>
-    <t>VA-11.12</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -474,21 +222,9 @@
     <t>Mùi</t>
   </si>
   <si>
-    <t>Nguyễn Quý</t>
-  </si>
-  <si>
     <t>Ngô Quý</t>
   </si>
   <si>
-    <t>Nguyễn Lệnh</t>
-  </si>
-  <si>
-    <t>Nguyễn Nhất</t>
-  </si>
-  <si>
-    <t>Nguyễn Lục</t>
-  </si>
-  <si>
     <t>Mai</t>
   </si>
   <si>
@@ -570,222 +306,12 @@
     <t>Đăng</t>
   </si>
   <si>
-    <t>Nguyễn Thị</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Châu</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Xuân</t>
-  </si>
-  <si>
-    <t>Nguyễn Thùy</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồng</t>
-  </si>
-  <si>
-    <t>Nguyễn Thúy</t>
-  </si>
-  <si>
-    <t>Nguyễn Diệu</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Mai</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Kim</t>
-  </si>
-  <si>
-    <t>Nguyễn Phương</t>
-  </si>
-  <si>
-    <t>Nguyễn Thu</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Đức</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Khánh</t>
-  </si>
-  <si>
-    <t>Nguyễn Diệp</t>
-  </si>
-  <si>
-    <t>Nguyễn Thuỷ</t>
-  </si>
-  <si>
-    <t>Nguyễn Bảo</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Việt</t>
-  </si>
-  <si>
-    <t>Nguyễn Hiểu</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Hải</t>
-  </si>
-  <si>
-    <t>VA-5.01S1</t>
-  </si>
-  <si>
-    <t>VA-5.02S1</t>
-  </si>
-  <si>
-    <t>Nguyễn Quý Thị</t>
-  </si>
-  <si>
-    <t>VA-5.03S1</t>
-  </si>
-  <si>
-    <t>VA-5.06S1</t>
-  </si>
-  <si>
-    <t>VA-6.03S1</t>
-  </si>
-  <si>
-    <t>VA-6.04S1</t>
-  </si>
-  <si>
-    <t>VA-6.05S1</t>
-  </si>
-  <si>
-    <t>VA-6.06S1</t>
-  </si>
-  <si>
-    <t>VA-7.02S1</t>
-  </si>
-  <si>
-    <t>VA-7.03S1</t>
-  </si>
-  <si>
-    <t>VA-8.01S1</t>
-  </si>
-  <si>
-    <t>VA-8.02S1</t>
-  </si>
-  <si>
-    <t>VA-8.03S1</t>
-  </si>
-  <si>
-    <t>VA-8.04S1</t>
-  </si>
-  <si>
-    <t>VA-8.05S1</t>
-  </si>
-  <si>
-    <t>VA-8.07S1</t>
-  </si>
-  <si>
-    <t>VA-8.08S1</t>
-  </si>
-  <si>
-    <t>VA-8.09S1</t>
-  </si>
-  <si>
-    <t>VA-8.10S1</t>
-  </si>
-  <si>
-    <t>VA-9.02S1</t>
-  </si>
-  <si>
-    <t>VA-9.03S1</t>
-  </si>
-  <si>
-    <t>VA-9.04S1</t>
-  </si>
-  <si>
-    <t>VA-9.05S1</t>
-  </si>
-  <si>
-    <t>VA-9.06S1</t>
-  </si>
-  <si>
-    <t>VA-9.07S1</t>
-  </si>
-  <si>
-    <t>VA-9.08S1</t>
-  </si>
-  <si>
-    <t>VA-9.09S1</t>
-  </si>
-  <si>
-    <t>VA-9.10S1</t>
-  </si>
-  <si>
-    <t>VA-9.11S1</t>
-  </si>
-  <si>
-    <t>VA-9.12S1</t>
-  </si>
-  <si>
-    <t>VA-9.13S1</t>
-  </si>
-  <si>
-    <t>VA-9.14S1</t>
-  </si>
-  <si>
-    <t>VA-9.15S1</t>
-  </si>
-  <si>
-    <t>VA-9.16S1</t>
-  </si>
-  <si>
-    <t>VA-9.17S1</t>
-  </si>
-  <si>
-    <t>VA-9.18S1</t>
-  </si>
-  <si>
-    <t>VA-9.19S1</t>
-  </si>
-  <si>
-    <t>VA-10.01S1</t>
-  </si>
-  <si>
-    <t>VA-10.02S1</t>
-  </si>
-  <si>
-    <t>VA-10.03S1</t>
-  </si>
-  <si>
-    <t>VA-10.04S1</t>
-  </si>
-  <si>
-    <t>VA-10.05S1</t>
-  </si>
-  <si>
-    <t>VA-10.06S1</t>
-  </si>
-  <si>
-    <t>VA-10.08S1</t>
-  </si>
-  <si>
-    <t>VA-10.10S1</t>
-  </si>
-  <si>
-    <t>VA-10.09S1</t>
-  </si>
-  <si>
-    <t>VA-10.11S1</t>
-  </si>
-  <si>
     <t>Hội</t>
   </si>
   <si>
     <t>Hoa</t>
   </si>
   <si>
-    <t>Nguyễn Công</t>
-  </si>
-  <si>
     <t>Phiếu</t>
   </si>
   <si>
@@ -828,9 +354,6 @@
     <t>Hợi</t>
   </si>
   <si>
-    <t>Nguyễn Đức</t>
-  </si>
-  <si>
     <t>Thắng</t>
   </si>
   <si>
@@ -846,15 +369,9 @@
     <t>Hà</t>
   </si>
   <si>
-    <t>Nguyễn Bách</t>
-  </si>
-  <si>
     <t>Dư</t>
   </si>
   <si>
-    <t>Nguyễn Văn</t>
-  </si>
-  <si>
     <t>Vinh</t>
   </si>
   <si>
@@ -864,9 +381,6 @@
     <t>Diệp</t>
   </si>
   <si>
-    <t>Nguyễn Ngọc</t>
-  </si>
-  <si>
     <t>Đỗ Văn</t>
   </si>
   <si>
@@ -885,15 +399,9 @@
     <t>Việt</t>
   </si>
   <si>
-    <t>Nguyễn Đắc</t>
-  </si>
-  <si>
     <t>Mậu</t>
   </si>
   <si>
-    <t>Nguyễn Thanh</t>
-  </si>
-  <si>
     <t>Thúy</t>
   </si>
   <si>
@@ -909,12 +417,6 @@
     <t>Nhàn</t>
   </si>
   <si>
-    <t>Nguyễn Việt</t>
-  </si>
-  <si>
-    <t>Nguyễn Tiến</t>
-  </si>
-  <si>
     <t>Đạt</t>
   </si>
   <si>
@@ -942,21 +444,12 @@
     <t>tin</t>
   </si>
   <si>
-    <t>VA-10.02S2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bùi Thị </t>
   </si>
   <si>
     <t>đã ly hôn</t>
   </si>
   <si>
-    <t>VA-11.08S1</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh</t>
-  </si>
-  <si>
     <t>Nhật</t>
   </si>
   <si>
@@ -972,12 +465,6 @@
     <t>Diệu Quang</t>
   </si>
   <si>
-    <t>Con: Nguyễn Thị Uyên; Nguyễn Thị Quan</t>
-  </si>
-  <si>
-    <t>VA-7.02S2</t>
-  </si>
-  <si>
     <t>Quặm</t>
   </si>
   <si>
@@ -987,18 +474,9 @@
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t>con: Lê Duy Tuấn</t>
-  </si>
-  <si>
-    <t>con: Lưu Bách Dũng, Lưu Bách Hải</t>
-  </si>
-  <si>
     <t>Phượng</t>
   </si>
   <si>
-    <t>con: Lưu Bách Mắn, May, Dậu</t>
-  </si>
-  <si>
     <t>MID</t>
   </si>
   <si>
@@ -1029,12 +507,6 @@
     <t>23/07</t>
   </si>
   <si>
-    <t>M0001</t>
-  </si>
-  <si>
-    <t>M0002</t>
-  </si>
-  <si>
     <t>ly hôn</t>
   </si>
   <si>
@@ -1047,12 +519,6 @@
     <t>kết hôn</t>
   </si>
   <si>
-    <t>M0003</t>
-  </si>
-  <si>
-    <t>M0004</t>
-  </si>
-  <si>
     <t>bà cả</t>
   </si>
   <si>
@@ -1104,81 +570,18 @@
     <t>Làm tại ABC</t>
   </si>
   <si>
-    <t>M0005</t>
-  </si>
-  <si>
-    <t>M0006</t>
-  </si>
-  <si>
     <t>M0007</t>
   </si>
   <si>
     <t>M0008</t>
   </si>
   <si>
-    <t>M0009</t>
-  </si>
-  <si>
-    <t>M0010</t>
-  </si>
-  <si>
-    <t>M0011</t>
-  </si>
-  <si>
-    <t>M0012</t>
-  </si>
-  <si>
-    <t>M0013</t>
-  </si>
-  <si>
-    <t>M0014</t>
-  </si>
-  <si>
-    <t>M0015</t>
-  </si>
-  <si>
-    <t>M0016</t>
-  </si>
-  <si>
-    <t>M0017</t>
-  </si>
-  <si>
-    <t>M0018</t>
-  </si>
-  <si>
-    <t>M0019</t>
-  </si>
-  <si>
-    <t>M0020</t>
-  </si>
-  <si>
-    <t>M0021</t>
-  </si>
-  <si>
-    <t>M0022</t>
-  </si>
-  <si>
-    <t>M0023</t>
-  </si>
-  <si>
     <t>M0024</t>
   </si>
   <si>
     <t>M0025</t>
   </si>
   <si>
-    <t>M0026</t>
-  </si>
-  <si>
-    <t>M0027</t>
-  </si>
-  <si>
-    <t>M0028</t>
-  </si>
-  <si>
-    <t>M0029</t>
-  </si>
-  <si>
     <t>M0030</t>
   </si>
   <si>
@@ -1218,303 +621,6 @@
     <t>chân dung 2</t>
   </si>
   <si>
-    <t>mất ngày 09/08/2026 tức 27/06</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.01.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.01S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.02.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.02S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.03.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.03S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.04.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.04S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.05.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.07.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.07S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.08.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.09.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.09S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.10.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-8.10S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.01.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.02.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.02S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.03.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.03S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.04.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.04S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.05.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.05S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.06.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.06S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.07.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.07S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.08.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.08S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.09.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.09S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.10.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.10S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.11.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.11S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.12.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.12S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.13.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.13S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.14.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.14S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.15.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.15S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.16.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.17.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.17S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.18.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.18S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.19.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-9.19S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.01.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.01S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.02.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.02S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.03.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.03S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.04.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.04S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.05.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.05S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.06.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.06S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.07.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.08.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.08S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.09.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.09S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.10.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.10S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.11.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.11S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.12.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.13.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.14.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.15.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.16.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.17.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.18.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.19.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.20.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-10.21.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.01.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.02.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.03.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.04.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.05.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.06.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.07.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.08.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.08S1.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.09.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.10.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.11.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/VA-11.12.jpg</t>
-  </si>
-  <si>
-    <t>images/persons/CAOPHOVA807.jpg</t>
-  </si>
-  <si>
-    <t>Cáo Phó</t>
-  </si>
-  <si>
     <t>27/06/2026</t>
   </si>
   <si>
@@ -1527,15 +633,9 @@
     <t>Giỗ Cụ Ngô Quý Thị, Hiệu Từ Liễn</t>
   </si>
   <si>
-    <t>Giỗ cụ Thuỷ Tổ. Tự Phúc Bằng</t>
-  </si>
-  <si>
     <t>15/02</t>
   </si>
   <si>
-    <t>Giỗ cụ bà Nguyễn Thị Hoa, hiệu Diệu Quang</t>
-  </si>
-  <si>
     <t>Phúc Tuất</t>
   </si>
   <si>
@@ -1557,15 +657,6 @@
     <t>13/08</t>
   </si>
   <si>
-    <t>Giỗ cụ Nguyễn Quý Công , Tự Phúc Tuất</t>
-  </si>
-  <si>
-    <t>Xuân Thuỳ con cụ Chiến,  chết sớm, giỗ 23/07 âm lịch</t>
-  </si>
-  <si>
-    <t>Ông Độ, Pháp danh Minh Phúc, Chết 15/07/2021 thọ 66 tuổi</t>
-  </si>
-  <si>
     <t>23/02</t>
   </si>
   <si>
@@ -1575,18 +666,9 @@
     <t>03/06</t>
   </si>
   <si>
-    <t>Cụ Phúc Thảo,  pháp danh Minh Hiền</t>
-  </si>
-  <si>
-    <t>Cụ Phúc Tích, Chết 15/11/2014 thọ 89 tuổi</t>
-  </si>
-  <si>
     <t>29/01</t>
   </si>
   <si>
-    <t>cụ Phúc Đào, pháp danh Liễu Ngộ</t>
-  </si>
-  <si>
     <t>29/04</t>
   </si>
   <si>
@@ -1599,9 +681,6 @@
     <t>Cụ Bà Đào, Pháp danh Diệu Hà,</t>
   </si>
   <si>
-    <t>Nguyễn Phúc Lan, Tự Thuần Tuệ  (chết trẻ )</t>
-  </si>
-  <si>
     <t>Ông Bích, Pháp danh Minh Định, Chết 28/08/2021 thọ 68 tuổi</t>
   </si>
   <si>
@@ -1620,15 +699,9 @@
     <t>cụ Bào, vợ cụ Cốc</t>
   </si>
   <si>
-    <t>Tự Thuần Ban, giỗ 15/10 ?</t>
-  </si>
-  <si>
     <t>Giỗ 15/07 ?</t>
   </si>
   <si>
-    <t>tên Tự : Thuần Bản ( theo ds cúng giỗ) ?</t>
-  </si>
-  <si>
     <t>15/10</t>
   </si>
   <si>
@@ -1650,9 +723,6 @@
     <t>12/11/1977</t>
   </si>
   <si>
-    <t>Nguyễn Quý Công Tự Phúc Cốc. Chết 12/11/1977 Đinh Tỵ , thọ 73 tuổi</t>
-  </si>
-  <si>
     <t>Giỗ 12/11 Đinh Tỵ</t>
   </si>
   <si>
@@ -1674,54 +744,18 @@
     <t>Giỗ 13/08</t>
   </si>
   <si>
-    <t>images/3ba.jpg</t>
-  </si>
-  <si>
     <t>images/Backdrop2026.jpg</t>
   </si>
   <si>
-    <t>images/CacBa.jpg</t>
-  </si>
-  <si>
-    <t>Ảnh tập thể</t>
-  </si>
-  <si>
     <t>Background 2026</t>
   </si>
   <si>
-    <t>images/ChiVinhAn.jpg</t>
-  </si>
-  <si>
-    <t>images/XuanHien.jpg</t>
-  </si>
-  <si>
-    <t>Ảnh gia đình</t>
-  </si>
-  <si>
-    <t>images/BatTay.jpg</t>
-  </si>
-  <si>
-    <t>Bắt tay giữa Xuân Đông và Xuân Trường</t>
-  </si>
-  <si>
     <t>Trần</t>
   </si>
   <si>
     <t>Chanh</t>
   </si>
   <si>
-    <t>images/ConTraiVA.jpg</t>
-  </si>
-  <si>
-    <t>images/MoToVA.jpg</t>
-  </si>
-  <si>
-    <t>Ảnh Mộ Tổ Phúc Bằng</t>
-  </si>
-  <si>
-    <t>Tập thể Nam</t>
-  </si>
-  <si>
     <t>Sơ đồ chi vĩnh an</t>
   </si>
   <si>
@@ -1744,6 +778,549 @@
   </si>
   <si>
     <t>images/about/chi-vinh-an.jpg</t>
+  </si>
+  <si>
+    <t>Đỗ Việt</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Đức</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Phúc</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Khánh</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Việt</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Minh</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Hải</t>
+  </si>
+  <si>
+    <t>Đỗ Quý</t>
+  </si>
+  <si>
+    <t>Đỗ Lệnh</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Quý</t>
+  </si>
+  <si>
+    <t>Đỗ Nhất</t>
+  </si>
+  <si>
+    <t>Đỗ Lục</t>
+  </si>
+  <si>
+    <t>Đỗ Quý Thị</t>
+  </si>
+  <si>
+    <t>Đỗ Thị</t>
+  </si>
+  <si>
+    <t>Con: Đỗ Thị Uyên; Đỗ Thị Quan</t>
+  </si>
+  <si>
+    <t>Đỗ Công</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Châu</t>
+  </si>
+  <si>
+    <t>Đỗ Đức</t>
+  </si>
+  <si>
+    <t>Đỗ Bách</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Xuân</t>
+  </si>
+  <si>
+    <t>Đỗ Ngọc</t>
+  </si>
+  <si>
+    <t>Đỗ Đắc</t>
+  </si>
+  <si>
+    <t>Đỗ Thu</t>
+  </si>
+  <si>
+    <t>Đỗ Thanh</t>
+  </si>
+  <si>
+    <t>Đỗ Thùy</t>
+  </si>
+  <si>
+    <t>Đỗ Hồng</t>
+  </si>
+  <si>
+    <t>Đỗ Thúy</t>
+  </si>
+  <si>
+    <t>Đỗ Diệu</t>
+  </si>
+  <si>
+    <t>Đỗ Tiến</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Mai</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Kim</t>
+  </si>
+  <si>
+    <t>Đỗ Phương</t>
+  </si>
+  <si>
+    <t>Đỗ Diệp</t>
+  </si>
+  <si>
+    <t>Đỗ Thuỷ</t>
+  </si>
+  <si>
+    <t>Đỗ Bảo</t>
+  </si>
+  <si>
+    <t>Đỗ Anh</t>
+  </si>
+  <si>
+    <t>Đỗ Minh</t>
+  </si>
+  <si>
+    <t>Đỗ Hiểu</t>
+  </si>
+  <si>
+    <t>con: Mắn, May, Dậu</t>
+  </si>
+  <si>
+    <t>TV-7.02</t>
+  </si>
+  <si>
+    <t>TV-7.02S1</t>
+  </si>
+  <si>
+    <t>TV-7.02S2</t>
+  </si>
+  <si>
+    <t>TV-10.02</t>
+  </si>
+  <si>
+    <t>TV-10.02S1</t>
+  </si>
+  <si>
+    <t>TV-10.02S2</t>
+  </si>
+  <si>
+    <t>TV-11.08S1</t>
+  </si>
+  <si>
+    <t>TV-11.08</t>
+  </si>
+  <si>
+    <t>TV-4.02</t>
+  </si>
+  <si>
+    <t>TV-4.02S1</t>
+  </si>
+  <si>
+    <t>TV-5.01</t>
+  </si>
+  <si>
+    <t>TV-5.01S1</t>
+  </si>
+  <si>
+    <t>TV-5.02</t>
+  </si>
+  <si>
+    <t>TV-5.02S1</t>
+  </si>
+  <si>
+    <t>TV-5.03</t>
+  </si>
+  <si>
+    <t>TV-5.03S1</t>
+  </si>
+  <si>
+    <t>TV-5.04</t>
+  </si>
+  <si>
+    <t>TV-5.05</t>
+  </si>
+  <si>
+    <t>TV-5.06</t>
+  </si>
+  <si>
+    <t>TV-5.06S1</t>
+  </si>
+  <si>
+    <t>TV-6.01</t>
+  </si>
+  <si>
+    <t>TV-6.02</t>
+  </si>
+  <si>
+    <t>TV-6.03</t>
+  </si>
+  <si>
+    <t>TV-6.03S1</t>
+  </si>
+  <si>
+    <t>TV-6.04</t>
+  </si>
+  <si>
+    <t>TV-6.04S1</t>
+  </si>
+  <si>
+    <t>TV-6.05</t>
+  </si>
+  <si>
+    <t>TV-6.05S1</t>
+  </si>
+  <si>
+    <t>TV-6.06</t>
+  </si>
+  <si>
+    <t>TV-6.06S1</t>
+  </si>
+  <si>
+    <t>TV-7.01</t>
+  </si>
+  <si>
+    <t>TV-7.03</t>
+  </si>
+  <si>
+    <t>TV-7.03S1</t>
+  </si>
+  <si>
+    <t>TV-8.01</t>
+  </si>
+  <si>
+    <t>TV-8.01S1</t>
+  </si>
+  <si>
+    <t>TV-8.02</t>
+  </si>
+  <si>
+    <t>TV-8.02S1</t>
+  </si>
+  <si>
+    <t>TV-8.03</t>
+  </si>
+  <si>
+    <t>TV-8.03S1</t>
+  </si>
+  <si>
+    <t>TV-8.04</t>
+  </si>
+  <si>
+    <t>TV-8.04S1</t>
+  </si>
+  <si>
+    <t>TV-8.05</t>
+  </si>
+  <si>
+    <t>TV-8.05S1</t>
+  </si>
+  <si>
+    <t>TV-8.06</t>
+  </si>
+  <si>
+    <t>TV-8.07</t>
+  </si>
+  <si>
+    <t>TV-8.07S1</t>
+  </si>
+  <si>
+    <t>TV-8.08</t>
+  </si>
+  <si>
+    <t>TV-8.08S1</t>
+  </si>
+  <si>
+    <t>TV-8.09</t>
+  </si>
+  <si>
+    <t>TV-8.09S1</t>
+  </si>
+  <si>
+    <t>TV-8.10</t>
+  </si>
+  <si>
+    <t>TV-8.10S1</t>
+  </si>
+  <si>
+    <t>TV-9.01</t>
+  </si>
+  <si>
+    <t>TV-9.02</t>
+  </si>
+  <si>
+    <t>TV-9.02S1</t>
+  </si>
+  <si>
+    <t>TV-9.03</t>
+  </si>
+  <si>
+    <t>TV-9.03S1</t>
+  </si>
+  <si>
+    <t>TV-9.04</t>
+  </si>
+  <si>
+    <t>TV-9.04S1</t>
+  </si>
+  <si>
+    <t>TV-9.05</t>
+  </si>
+  <si>
+    <t>TV-9.05S1</t>
+  </si>
+  <si>
+    <t>TV-9.06</t>
+  </si>
+  <si>
+    <t>TV-9.06S1</t>
+  </si>
+  <si>
+    <t>TV-9.07</t>
+  </si>
+  <si>
+    <t>TV-9.07S1</t>
+  </si>
+  <si>
+    <t>TV-9.08</t>
+  </si>
+  <si>
+    <t>TV-9.08S1</t>
+  </si>
+  <si>
+    <t>TV-9.09</t>
+  </si>
+  <si>
+    <t>TV-9.09S1</t>
+  </si>
+  <si>
+    <t>TV-9.10</t>
+  </si>
+  <si>
+    <t>TV-9.10S1</t>
+  </si>
+  <si>
+    <t>TV-9.11</t>
+  </si>
+  <si>
+    <t>TV-9.11S1</t>
+  </si>
+  <si>
+    <t>TV-9.12</t>
+  </si>
+  <si>
+    <t>TV-9.12S1</t>
+  </si>
+  <si>
+    <t>TV-9.13</t>
+  </si>
+  <si>
+    <t>TV-9.13S1</t>
+  </si>
+  <si>
+    <t>TV-9.14</t>
+  </si>
+  <si>
+    <t>TV-9.14S1</t>
+  </si>
+  <si>
+    <t>TV-9.15</t>
+  </si>
+  <si>
+    <t>TV-9.15S1</t>
+  </si>
+  <si>
+    <t>TV-9.16</t>
+  </si>
+  <si>
+    <t>TV-9.16S1</t>
+  </si>
+  <si>
+    <t>TV-9.17</t>
+  </si>
+  <si>
+    <t>TV-9.17S1</t>
+  </si>
+  <si>
+    <t>TV-9.18</t>
+  </si>
+  <si>
+    <t>TV-9.18S1</t>
+  </si>
+  <si>
+    <t>TV-9.19</t>
+  </si>
+  <si>
+    <t>TV-9.19S1</t>
+  </si>
+  <si>
+    <t>TV-9.20</t>
+  </si>
+  <si>
+    <t>TV-10.01</t>
+  </si>
+  <si>
+    <t>TV-10.01S1</t>
+  </si>
+  <si>
+    <t>images/persons/TV-10.02.jpg</t>
+  </si>
+  <si>
+    <t>TV-10.03</t>
+  </si>
+  <si>
+    <t>TV-10.03S1</t>
+  </si>
+  <si>
+    <t>TV-10.04</t>
+  </si>
+  <si>
+    <t>TV-10.04S1</t>
+  </si>
+  <si>
+    <t>TV-10.05</t>
+  </si>
+  <si>
+    <t>TV-10.05S1</t>
+  </si>
+  <si>
+    <t>TV-10.06</t>
+  </si>
+  <si>
+    <t>TV-10.06S1</t>
+  </si>
+  <si>
+    <t>TV-10.07</t>
+  </si>
+  <si>
+    <t>TV-10.08</t>
+  </si>
+  <si>
+    <t>TV-10.08S1</t>
+  </si>
+  <si>
+    <t>TV-10.09</t>
+  </si>
+  <si>
+    <t>TV-10.09S1</t>
+  </si>
+  <si>
+    <t>TV-10.10</t>
+  </si>
+  <si>
+    <t>TV-10.10S1</t>
+  </si>
+  <si>
+    <t>TV-10.11</t>
+  </si>
+  <si>
+    <t>TV-10.11S1</t>
+  </si>
+  <si>
+    <t>TV-10.12</t>
+  </si>
+  <si>
+    <t>TV-10.13</t>
+  </si>
+  <si>
+    <t>TV-10.14</t>
+  </si>
+  <si>
+    <t>TV-10.15</t>
+  </si>
+  <si>
+    <t>TV-10.16</t>
+  </si>
+  <si>
+    <t>TV-10.17</t>
+  </si>
+  <si>
+    <t>TV-10.18</t>
+  </si>
+  <si>
+    <t>TV-10.19</t>
+  </si>
+  <si>
+    <t>TV-10.20</t>
+  </si>
+  <si>
+    <t>TV-10.21</t>
+  </si>
+  <si>
+    <t>TV-11.01</t>
+  </si>
+  <si>
+    <t>TV-11.02</t>
+  </si>
+  <si>
+    <t>TV-11.03</t>
+  </si>
+  <si>
+    <t>TV-11.04</t>
+  </si>
+  <si>
+    <t>TV-11.05</t>
+  </si>
+  <si>
+    <t>TV-11.06</t>
+  </si>
+  <si>
+    <t>TV-11.07</t>
+  </si>
+  <si>
+    <t>TV-11.09</t>
+  </si>
+  <si>
+    <t>TV-11.10</t>
+  </si>
+  <si>
+    <t>TV-11.11</t>
+  </si>
+  <si>
+    <t>TV-11.12</t>
+  </si>
+  <si>
+    <t>Văn</t>
+  </si>
+  <si>
+    <t>Giỗ cụ bà Đỗ Thị Hoa, hiệu Diệu Quang</t>
+  </si>
+  <si>
+    <t>Giỗ cụ Thuỷ Tổ. Tự Việt Bằng</t>
+  </si>
+  <si>
+    <t>Đỗ Quý Công Tự Việt Cốc. Chết 12/11/1977 Đinh Tỵ , thọ 73 tuổi</t>
+  </si>
+  <si>
+    <t>Giỗ cụ Đỗ Quý Công , Tự Việt Tuất</t>
+  </si>
+  <si>
+    <t>Cụ Việt Tích, Chết 15/11/2014 thọ 89 tuổi</t>
+  </si>
+  <si>
+    <t>Ông Độ, Pháp danh Minh Việt, Chết 15/07/2021 thọ 66 tuổi</t>
+  </si>
+  <si>
+    <t>Đỗ Việt Lan, Tự Thuần Tuệ  (chết trẻ )</t>
+  </si>
+  <si>
+    <t>Cụ Việt Thảo,  pháp danh Minh Hiền</t>
+  </si>
+  <si>
+    <t>cụ Việt Đào, pháp danh Liễu Ngộ</t>
+  </si>
+  <si>
+    <t>Việt Thuỳ con cụ Chiến,  chết sớm, giỗ 23/07 âm lịch</t>
   </si>
 </sst>
 </file>
@@ -1964,9 +1541,9 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2301,19 +1878,19 @@
   <sheetData>
     <row r="1" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -2331,10 +1908,10 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>343</v>
+        <v>165</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
@@ -2345,19 +1922,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2">
@@ -2376,19 +1953,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" s="19"/>
       <c r="H3" s="19">
@@ -2407,29 +1984,29 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2">
         <v>1900</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -2442,17 +2019,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>30</v>
+        <v>254</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>244</v>
+        <v>87</v>
       </c>
       <c r="E5" s="19"/>
       <c r="F5" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="18">
@@ -2471,29 +2048,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>296</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2">
         <v>1900</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -2506,19 +2083,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>197</v>
+        <v>297</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>307</v>
+        <v>138</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7" s="19"/>
       <c r="H7" s="18">
@@ -2528,7 +2105,7 @@
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18" t="s">
-        <v>526</v>
+        <v>218</v>
       </c>
       <c r="M7" s="17">
         <v>5</v>
@@ -2539,34 +2116,32 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2">
         <v>1900</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="2" t="s">
-        <v>527</v>
-      </c>
+      <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
@@ -2576,17 +2151,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>199</v>
+        <v>299</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>298</v>
+        <v>132</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="18">
@@ -2605,33 +2180,33 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>146</v>
+        <v>255</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2">
         <v>1900</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="M10" s="2">
         <v>5</v>
@@ -2642,33 +2217,33 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2">
         <v>1900</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="M11" s="2">
         <v>5</v>
@@ -2679,34 +2254,32 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>302</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2">
         <v>1900</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="2" t="s">
-        <v>525</v>
-      </c>
+      <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
@@ -2716,19 +2289,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>245</v>
+        <v>88</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>308</v>
+        <v>139</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="18">
@@ -2747,33 +2320,33 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>304</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2">
         <v>1900</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="M14" s="2">
         <v>6</v>
@@ -2784,33 +2357,33 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2">
         <v>1900</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="M15" s="2">
         <v>6</v>
@@ -2821,31 +2394,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>306</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2">
         <v>1900</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="M16" s="2">
         <v>6</v>
@@ -2856,17 +2429,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>247</v>
+        <v>89</v>
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="18">
@@ -2885,27 +2458,27 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>308</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2">
         <v>1900</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>199</v>
+        <v>299</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -2918,17 +2491,17 @@
         <v>18</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>202</v>
+        <v>309</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>298</v>
+        <v>132</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="18">
@@ -2947,33 +2520,33 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>310</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>497</v>
+        <v>197</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2">
         <v>1900</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>22</v>
+        <v>302</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2" t="s">
-        <v>542</v>
+        <v>232</v>
       </c>
       <c r="M20" s="2">
         <v>6</v>
@@ -2984,17 +2557,17 @@
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>538</v>
+        <v>228</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>539</v>
+        <v>229</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="18">
@@ -3004,7 +2577,7 @@
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
       <c r="L21" s="18" t="s">
-        <v>537</v>
+        <v>227</v>
       </c>
       <c r="M21" s="17">
         <v>6</v>
@@ -3015,28 +2588,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>312</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>305</v>
+        <v>136</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2">
         <v>1900</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>22</v>
+        <v>302</v>
       </c>
       <c r="J22" s="2" t="str">
         <f>I22&amp;"S1"</f>
-        <v>VA-5.06S1</v>
+        <v>TV-5.06S1</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -3049,17 +2622,17 @@
         <v>22</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>248</v>
+        <v>90</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="18">
@@ -3078,27 +2651,27 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>33</v>
+        <v>314</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>177</v>
+        <v>261</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2">
         <v>1900</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>202</v>
+        <v>309</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>29</v>
+        <v>308</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -3111,19 +2684,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>498</v>
+        <v>198</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25" s="2">
         <v>1904</v>
@@ -3132,15 +2705,15 @@
         <v>1977</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>31</v>
+        <v>310</v>
       </c>
       <c r="J25" s="2" t="str">
         <f>I25&amp;"S1"</f>
-        <v>VA-6.05S1</v>
+        <v>TV-6.05S1</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
-        <v>536</v>
+        <v>226</v>
       </c>
       <c r="M25" s="2">
         <v>7</v>
@@ -3151,17 +2724,17 @@
         <v>25</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="18"/>
@@ -3169,7 +2742,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18" t="s">
-        <v>521</v>
+        <v>214</v>
       </c>
       <c r="M26" s="17">
         <v>7</v>
@@ -3180,17 +2753,17 @@
         <v>26</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>311</v>
+        <v>140</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
         <v>1912</v>
@@ -3202,7 +2775,7 @@
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="18" t="s">
-        <v>531</v>
+        <v>222</v>
       </c>
       <c r="M27" s="17">
         <v>7</v>
@@ -3213,29 +2786,29 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>35</v>
+        <v>315</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>31</v>
+        <v>310</v>
       </c>
       <c r="J28" s="2" t="str">
         <f>I28&amp;"S1"</f>
-        <v>VA-6.05S1</v>
+        <v>TV-6.05S1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>341</v>
+        <v>163</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
@@ -3247,17 +2820,17 @@
         <v>28</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>206</v>
+        <v>316</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="18"/>
@@ -3274,19 +2847,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>499</v>
+        <v>199</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G30" s="3">
         <v>1926</v>
@@ -3295,14 +2868,12 @@
         <v>2015</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>392</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3">
         <v>8</v>
@@ -3313,17 +2884,17 @@
         <v>30</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>207</v>
+        <v>318</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>252</v>
+        <v>94</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G31" s="16">
         <v>1922</v>
@@ -3333,9 +2904,7 @@
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
-      <c r="K31" s="18" t="s">
-        <v>393</v>
-      </c>
+      <c r="K31" s="18"/>
       <c r="L31" s="18"/>
       <c r="M31" s="17">
         <v>8</v>
@@ -3346,33 +2915,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" s="4">
         <v>1928</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>394</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3">
         <v>8</v>
@@ -3383,25 +2950,23 @@
         <v>32</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>208</v>
+        <v>320</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="E33" s="16"/>
       <c r="F33" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
-      <c r="K33" s="18" t="s">
-        <v>395</v>
-      </c>
+      <c r="K33" s="18"/>
       <c r="L33" s="18"/>
       <c r="M33" s="17">
         <v>8</v>
@@ -3412,33 +2977,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>501</v>
+        <v>201</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" s="3">
         <v>1931</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>396</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3">
         <v>8</v>
@@ -3449,17 +3012,17 @@
         <v>34</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>255</v>
+        <v>97</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35" s="16">
         <v>1942</v>
@@ -3467,9 +3030,7 @@
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
-      <c r="K35" s="18" t="s">
-        <v>397</v>
-      </c>
+      <c r="K35" s="18"/>
       <c r="L35" s="18"/>
       <c r="M35" s="17">
         <v>8</v>
@@ -3480,35 +3041,33 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>323</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>502</v>
+        <v>202</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>313</v>
+        <v>142</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>398</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>520</v>
+        <v>213</v>
       </c>
       <c r="M36" s="3">
         <v>8</v>
@@ -3519,25 +3078,23 @@
         <v>36</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>210</v>
+        <v>324</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>297</v>
+        <v>131</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>298</v>
+        <v>132</v>
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
-      <c r="K37" s="18" t="s">
-        <v>399</v>
-      </c>
+      <c r="K37" s="18"/>
       <c r="L37" s="18"/>
       <c r="M37" s="17">
         <v>8</v>
@@ -3548,31 +3105,29 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>40</v>
+        <v>325</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>400</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="M38" s="3">
         <v>8</v>
@@ -3583,17 +3138,17 @@
         <v>38</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>211</v>
+        <v>326</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>256</v>
+        <v>98</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>257</v>
+        <v>99</v>
       </c>
       <c r="E39" s="16"/>
       <c r="F39" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" s="16"/>
       <c r="H39" s="18"/>
@@ -3610,25 +3165,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
@@ -3641,17 +3196,17 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>328</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41" s="3">
         <v>1944</v>
@@ -3660,17 +3215,13 @@
         <v>2026</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>391</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="3">
         <v>8</v>
       </c>
@@ -3680,17 +3231,17 @@
         <v>41</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>212</v>
+        <v>329</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>258</v>
+        <v>100</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>259</v>
+        <v>101</v>
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G42" s="16">
         <v>1951</v>
@@ -3698,9 +3249,7 @@
       <c r="H42" s="18"/>
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
-      <c r="K42" s="18" t="s">
-        <v>402</v>
-      </c>
+      <c r="K42" s="18"/>
       <c r="L42" s="18"/>
       <c r="M42" s="17">
         <v>8</v>
@@ -3711,31 +3260,29 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="3">
         <v>1946</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>403</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3">
         <v>8</v>
@@ -3746,17 +3293,17 @@
         <v>43</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>213</v>
+        <v>331</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="E44" s="16"/>
       <c r="F44" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G44" s="16"/>
       <c r="H44" s="18"/>
@@ -3773,32 +3320,28 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>44</v>
+        <v>332</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>314</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="3">
         <v>8</v>
       </c>
@@ -3808,25 +3351,23 @@
         <v>45</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>214</v>
+        <v>333</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>262</v>
+        <v>103</v>
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G46" s="16"/>
       <c r="H46" s="18"/>
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
-      <c r="K46" s="18" t="s">
-        <v>405</v>
-      </c>
+      <c r="K46" s="18"/>
       <c r="L46" s="18"/>
       <c r="M46" s="17">
         <v>8</v>
@@ -3837,32 +3378,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>45</v>
+        <v>334</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>315</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="3">
         <v>8</v>
       </c>
@@ -3872,25 +3409,23 @@
         <v>47</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>256</v>
+        <v>98</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>263</v>
+        <v>104</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G48" s="16"/>
       <c r="H48" s="18"/>
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
-      <c r="K48" s="18" t="s">
-        <v>407</v>
-      </c>
+      <c r="K48" s="18"/>
       <c r="L48" s="18"/>
       <c r="M48" s="17">
         <v>8</v>
@@ -3901,31 +3436,29 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>46</v>
+        <v>336</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G49" s="5">
         <v>1952</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>408</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5">
         <v>9</v>
@@ -3936,31 +3469,29 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>47</v>
+        <v>337</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G50" s="5">
         <v>1953</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>409</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5">
         <v>9</v>
@@ -3971,25 +3502,23 @@
         <v>50</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>264</v>
+        <v>105</v>
       </c>
       <c r="E51" s="21"/>
       <c r="F51" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G51" s="21"/>
       <c r="H51" s="18"/>
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
-      <c r="K51" s="18" t="s">
-        <v>410</v>
-      </c>
+      <c r="K51" s="18"/>
       <c r="L51" s="18"/>
       <c r="M51" s="17">
         <v>9</v>
@@ -4000,17 +3529,17 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52" s="5">
         <v>1954</v>
@@ -4019,14 +3548,12 @@
         <v>2021</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>411</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5">
         <v>9</v>
@@ -4037,17 +3564,17 @@
         <v>52</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="E53" s="21"/>
       <c r="F53" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G53" s="21">
         <v>1958</v>
@@ -4055,9 +3582,7 @@
       <c r="H53" s="18"/>
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
-      <c r="K53" s="18" t="s">
-        <v>412</v>
-      </c>
+      <c r="K53" s="18"/>
       <c r="L53" s="18"/>
       <c r="M53" s="17">
         <v>9</v>
@@ -4068,17 +3593,17 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>49</v>
+        <v>341</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" s="5">
         <v>1956</v>
@@ -4087,14 +3612,12 @@
         <v>2021</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>413</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5">
         <v>9</v>
@@ -4105,17 +3628,17 @@
         <v>54</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>218</v>
+        <v>342</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="E55" s="21"/>
       <c r="F55" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G55" s="21">
         <v>1959</v>
@@ -4123,9 +3646,7 @@
       <c r="H55" s="18"/>
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
-      <c r="K55" s="18" t="s">
-        <v>414</v>
-      </c>
+      <c r="K55" s="18"/>
       <c r="L55" s="18"/>
       <c r="M55" s="17">
         <v>9</v>
@@ -4136,31 +3657,29 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>50</v>
+        <v>343</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G56" s="5">
         <v>1958</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>415</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5">
         <v>9</v>
@@ -4171,25 +3690,23 @@
         <v>56</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>268</v>
+        <v>108</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G57" s="21"/>
       <c r="H57" s="18"/>
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
-      <c r="K57" s="18" t="s">
-        <v>416</v>
-      </c>
+      <c r="K57" s="18"/>
       <c r="L57" s="18"/>
       <c r="M57" s="17">
         <v>9</v>
@@ -4200,31 +3717,29 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>51</v>
+        <v>345</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G58" s="5">
         <v>1961</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>417</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K58" s="5"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5">
         <v>9</v>
@@ -4235,17 +3750,17 @@
         <v>58</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>220</v>
+        <v>346</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>270</v>
+        <v>109</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G59" s="21">
         <v>1955</v>
@@ -4253,9 +3768,7 @@
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
-      <c r="K59" s="18" t="s">
-        <v>418</v>
-      </c>
+      <c r="K59" s="18"/>
       <c r="L59" s="18"/>
       <c r="M59" s="17">
         <v>9</v>
@@ -4266,31 +3779,29 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>52</v>
+        <v>347</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G60" s="5">
         <v>1963</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>419</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5">
         <v>9</v>
@@ -4301,17 +3812,17 @@
         <v>60</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>221</v>
+        <v>348</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>271</v>
+        <v>110</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G61" s="21">
         <v>1969</v>
@@ -4319,9 +3830,7 @@
       <c r="H61" s="18"/>
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
-      <c r="K61" s="18" t="s">
-        <v>420</v>
-      </c>
+      <c r="K61" s="18"/>
       <c r="L61" s="18"/>
       <c r="M61" s="17">
         <v>9</v>
@@ -4332,31 +3841,29 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>53</v>
+        <v>349</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G62" s="5">
         <v>1965</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K62" s="5" t="s">
-        <v>421</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5">
         <v>9</v>
@@ -4367,25 +3874,23 @@
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>222</v>
+        <v>350</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="E63" s="21"/>
       <c r="F63" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G63" s="21"/>
       <c r="H63" s="18"/>
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
-      <c r="K63" s="18" t="s">
-        <v>422</v>
-      </c>
+      <c r="K63" s="18"/>
       <c r="L63" s="18"/>
       <c r="M63" s="17">
         <v>9</v>
@@ -4396,31 +3901,29 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>54</v>
+        <v>351</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G64" s="5">
         <v>1952</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K64" s="5" t="s">
-        <v>423</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5">
         <v>9</v>
@@ -4431,25 +3934,23 @@
         <v>64</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>272</v>
+        <v>111</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G65" s="21"/>
       <c r="H65" s="18"/>
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
-      <c r="K65" s="18" t="s">
-        <v>424</v>
-      </c>
+      <c r="K65" s="18"/>
       <c r="L65" s="18"/>
       <c r="M65" s="17">
         <v>9</v>
@@ -4460,31 +3961,29 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>55</v>
+        <v>353</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G66" s="5">
         <v>1962</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>425</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="K66" s="5"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5">
         <v>9</v>
@@ -4495,25 +3994,23 @@
         <v>66</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="E67" s="21"/>
       <c r="F67" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G67" s="21"/>
       <c r="H67" s="18"/>
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
-      <c r="K67" s="18" t="s">
-        <v>426</v>
-      </c>
+      <c r="K67" s="18"/>
       <c r="L67" s="18"/>
       <c r="M67" s="17">
         <v>9</v>
@@ -4524,31 +4021,29 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>56</v>
+        <v>355</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>178</v>
+        <v>264</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G68" s="5">
         <v>1965</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K68" s="5" t="s">
-        <v>427</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5">
         <v>9</v>
@@ -4559,25 +4054,23 @@
         <v>68</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>225</v>
+        <v>356</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G69" s="21"/>
       <c r="H69" s="18"/>
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
-      <c r="K69" s="18" t="s">
-        <v>428</v>
-      </c>
+      <c r="K69" s="18"/>
       <c r="L69" s="18"/>
       <c r="M69" s="17">
         <v>9</v>
@@ -4588,31 +4081,29 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>57</v>
+        <v>357</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G70" s="5">
         <v>1968</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>429</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5">
         <v>9</v>
@@ -4623,25 +4114,23 @@
         <v>70</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>274</v>
+        <v>112</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>275</v>
+        <v>113</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G71" s="21"/>
       <c r="H71" s="18"/>
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
-      <c r="K71" s="18" t="s">
-        <v>430</v>
-      </c>
+      <c r="K71" s="18"/>
       <c r="L71" s="18"/>
       <c r="M71" s="17">
         <v>9</v>
@@ -4652,31 +4141,29 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>58</v>
+        <v>359</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G72" s="5">
         <v>1972</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>431</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5">
         <v>9</v>
@@ -4687,25 +4174,23 @@
         <v>72</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>256</v>
+        <v>98</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>244</v>
+        <v>87</v>
       </c>
       <c r="E73" s="21"/>
       <c r="F73" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G73" s="21"/>
       <c r="H73" s="18"/>
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
-      <c r="K73" s="18" t="s">
-        <v>432</v>
-      </c>
+      <c r="K73" s="18"/>
       <c r="L73" s="18"/>
       <c r="M73" s="17">
         <v>9</v>
@@ -4716,31 +4201,29 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>59</v>
+        <v>361</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G74" s="5">
         <v>1975</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K74" s="5" t="s">
-        <v>433</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5">
         <v>9</v>
@@ -4751,17 +4234,17 @@
         <v>74</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>228</v>
+        <v>362</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>276</v>
+        <v>114</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="E75" s="21"/>
       <c r="F75" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G75" s="21">
         <v>1979</v>
@@ -4769,9 +4252,7 @@
       <c r="H75" s="18"/>
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
-      <c r="K75" s="18" t="s">
-        <v>434</v>
-      </c>
+      <c r="K75" s="18"/>
       <c r="L75" s="18"/>
       <c r="M75" s="17">
         <v>9</v>
@@ -4782,31 +4263,29 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>60</v>
+        <v>363</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G76" s="5">
         <v>1975</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5" t="s">
-        <v>42</v>
+        <v>328</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>435</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="K76" s="5"/>
       <c r="L76" s="5"/>
       <c r="M76" s="5">
         <v>9</v>
@@ -4817,17 +4296,17 @@
         <v>76</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>229</v>
+        <v>364</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G77" s="21">
         <v>1977</v>
@@ -4835,9 +4314,7 @@
       <c r="H77" s="18"/>
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
-      <c r="K77" s="18" t="s">
-        <v>436</v>
-      </c>
+      <c r="K77" s="18"/>
       <c r="L77" s="18"/>
       <c r="M77" s="17">
         <v>9</v>
@@ -4848,31 +4325,29 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>61</v>
+        <v>365</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G78" s="5">
         <v>1977</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5" t="s">
-        <v>42</v>
+        <v>328</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="K78" s="5" t="s">
-        <v>437</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="K78" s="5"/>
       <c r="L78" s="5"/>
       <c r="M78" s="5">
         <v>9</v>
@@ -4883,17 +4358,17 @@
         <v>78</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>230</v>
+        <v>366</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>553</v>
+        <v>235</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>554</v>
+        <v>236</v>
       </c>
       <c r="E79" s="21"/>
       <c r="F79" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G79" s="21"/>
       <c r="H79" s="18"/>
@@ -4910,31 +4385,29 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>62</v>
+        <v>367</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G80" s="5">
         <v>1970</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K80" s="5" t="s">
-        <v>438</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="K80" s="5"/>
       <c r="L80" s="5"/>
       <c r="M80" s="5">
         <v>9</v>
@@ -4945,25 +4418,23 @@
         <v>80</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>231</v>
+        <v>368</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="E81" s="21"/>
       <c r="F81" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G81" s="21"/>
       <c r="H81" s="18"/>
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
-      <c r="K81" s="18" t="s">
-        <v>439</v>
-      </c>
+      <c r="K81" s="18"/>
       <c r="L81" s="18"/>
       <c r="M81" s="17">
         <v>9</v>
@@ -4974,31 +4445,29 @@
         <v>81</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="E82" s="22"/>
       <c r="F82" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G82" s="22">
         <v>1972</v>
       </c>
       <c r="H82" s="22"/>
       <c r="I82" s="22" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K82" s="22" t="s">
-        <v>440</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="K82" s="22"/>
       <c r="L82" s="22"/>
       <c r="M82" s="22">
         <v>9</v>
@@ -5009,25 +4478,23 @@
         <v>82</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>232</v>
+        <v>370</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>279</v>
+        <v>117</v>
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G83" s="12"/>
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
-      <c r="K83" s="10" t="s">
-        <v>441</v>
-      </c>
+      <c r="K83" s="10"/>
       <c r="L83" s="10"/>
       <c r="M83" s="9">
         <v>9</v>
@@ -5038,31 +4505,29 @@
         <v>83</v>
       </c>
       <c r="B84" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D84" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G84" s="8">
         <v>1977</v>
       </c>
       <c r="H84" s="8"/>
       <c r="I84" s="8" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K84" s="8" t="s">
-        <v>442</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="K84" s="8"/>
       <c r="L84" s="8"/>
       <c r="M84" s="8">
         <v>9</v>
@@ -5073,25 +4538,23 @@
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>233</v>
+        <v>372</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>281</v>
+        <v>118</v>
       </c>
       <c r="E85" s="12"/>
       <c r="F85" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G85" s="12"/>
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
-      <c r="K85" s="10" t="s">
-        <v>443</v>
-      </c>
+      <c r="K85" s="10"/>
       <c r="L85" s="10"/>
       <c r="M85" s="9">
         <v>9</v>
@@ -5102,29 +4565,29 @@
         <v>85</v>
       </c>
       <c r="B86" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>153</v>
       </c>
       <c r="E86" s="8"/>
       <c r="F86" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
       <c r="I86" s="8" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>213</v>
+        <v>331</v>
       </c>
       <c r="K86" s="8"/>
       <c r="L86" s="8" t="s">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="M86" s="8">
         <v>9</v>
@@ -5135,31 +4598,29 @@
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D87" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G87" s="6">
         <v>1981</v>
       </c>
       <c r="H87" s="6"/>
       <c r="I87" s="6" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>444</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="K87" s="6"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6">
         <v>10</v>
@@ -5170,17 +4631,17 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>234</v>
+        <v>375</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="E88" s="9"/>
       <c r="F88" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G88" s="9">
         <v>1983</v>
@@ -5188,9 +4649,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
-      <c r="K88" s="10" t="s">
-        <v>445</v>
-      </c>
+      <c r="K88" s="10"/>
       <c r="L88" s="10"/>
       <c r="M88" s="9">
         <v>10</v>
@@ -5201,30 +4660,30 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>101</v>
+        <v>415</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G89" s="6">
         <v>1984</v>
       </c>
       <c r="H89" s="6"/>
       <c r="I89" s="6" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>446</v>
+        <v>376</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="6">
@@ -5236,17 +4695,17 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>283</v>
+        <v>119</v>
       </c>
       <c r="E90" s="13"/>
       <c r="F90" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G90" s="13">
         <v>1997</v>
@@ -5254,9 +4713,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
-      <c r="K90" s="10" t="s">
-        <v>447</v>
-      </c>
+      <c r="K90" s="10"/>
       <c r="L90" s="10"/>
       <c r="M90" s="9">
         <v>10</v>
@@ -5267,17 +4724,17 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>300</v>
+        <v>133</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="E91" s="13"/>
       <c r="F91" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G91" s="13">
         <v>1986</v>
@@ -5287,7 +4744,7 @@
       <c r="J91" s="10"/>
       <c r="K91" s="10"/>
       <c r="L91" s="10" t="s">
-        <v>301</v>
+        <v>134</v>
       </c>
       <c r="M91" s="9">
         <v>10</v>
@@ -5298,31 +4755,29 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>69</v>
+        <v>377</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="E92" s="6"/>
       <c r="F92" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G92" s="6">
         <v>1987</v>
       </c>
       <c r="H92" s="6"/>
       <c r="I92" s="6" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>448</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="K92" s="6"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6">
         <v>10</v>
@@ -5333,17 +4788,17 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>236</v>
+        <v>378</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>284</v>
+        <v>120</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>285</v>
+        <v>121</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G93" s="9">
         <v>1975</v>
@@ -5351,9 +4806,7 @@
       <c r="H93" s="10"/>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
-      <c r="K93" s="10" t="s">
-        <v>449</v>
-      </c>
+      <c r="K93" s="10"/>
       <c r="L93" s="10"/>
       <c r="M93" s="9">
         <v>10</v>
@@ -5364,31 +4817,29 @@
         <v>93</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G94" s="6">
         <v>1986</v>
       </c>
       <c r="H94" s="6"/>
       <c r="I94" s="6" t="s">
-        <v>49</v>
+        <v>341</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>450</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="K94" s="6"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6">
         <v>10</v>
@@ -5399,17 +4850,17 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>237</v>
+        <v>380</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>287</v>
+        <v>123</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G95" s="9">
         <v>1990</v>
@@ -5417,9 +4868,7 @@
       <c r="H95" s="10"/>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
-      <c r="K95" s="10" t="s">
-        <v>451</v>
-      </c>
+      <c r="K95" s="10"/>
       <c r="L95" s="10"/>
       <c r="M95" s="9">
         <v>10</v>
@@ -5430,31 +4879,29 @@
         <v>95</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>72</v>
+        <v>381</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>316</v>
+        <v>143</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G96" s="6">
         <v>1990</v>
       </c>
       <c r="H96" s="6"/>
       <c r="I96" s="6" t="s">
-        <v>49</v>
+        <v>341</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>452</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="K96" s="6"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6">
         <v>10</v>
@@ -5465,17 +4912,17 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>238</v>
+        <v>382</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G97" s="9">
         <v>1983</v>
@@ -5483,9 +4930,7 @@
       <c r="H97" s="10"/>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
-      <c r="K97" s="10" t="s">
-        <v>453</v>
-      </c>
+      <c r="K97" s="10"/>
       <c r="L97" s="10"/>
       <c r="M97" s="9">
         <v>10</v>
@@ -5496,31 +4941,29 @@
         <v>97</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>73</v>
+        <v>383</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G98" s="6">
         <v>1997</v>
       </c>
       <c r="H98" s="6"/>
       <c r="I98" s="6" t="s">
-        <v>52</v>
+        <v>347</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>454</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="K98" s="6"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6">
         <v>10</v>
@@ -5531,17 +4974,17 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>239</v>
+        <v>384</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G99" s="9">
         <v>1994</v>
@@ -5549,9 +4992,7 @@
       <c r="H99" s="10"/>
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
-      <c r="K99" s="10" t="s">
-        <v>455</v>
-      </c>
+      <c r="K99" s="10"/>
       <c r="L99" s="10"/>
       <c r="M99" s="9">
         <v>10</v>
@@ -5562,31 +5003,29 @@
         <v>99</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G100" s="6">
         <v>2000</v>
       </c>
       <c r="H100" s="6"/>
       <c r="I100" s="6" t="s">
-        <v>52</v>
+        <v>347</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>456</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="K100" s="6"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6">
         <v>10</v>
@@ -5597,31 +5036,29 @@
         <v>100</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>76</v>
+        <v>386</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G101" s="6">
         <v>1977</v>
       </c>
       <c r="H101" s="6"/>
       <c r="I101" s="6" t="s">
-        <v>54</v>
+        <v>351</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>457</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="K101" s="6"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6">
         <v>10</v>
@@ -5632,17 +5069,17 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>240</v>
+        <v>387</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>291</v>
+        <v>125</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>292</v>
+        <v>126</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G102" s="9">
         <v>1979</v>
@@ -5650,9 +5087,7 @@
       <c r="H102" s="10"/>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
-      <c r="K102" s="10" t="s">
-        <v>458</v>
-      </c>
+      <c r="K102" s="10"/>
       <c r="L102" s="10"/>
       <c r="M102" s="9">
         <v>10</v>
@@ -5663,31 +5098,29 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G103" s="6">
         <v>1981</v>
       </c>
       <c r="H103" s="6"/>
       <c r="I103" s="6" t="s">
-        <v>54</v>
+        <v>351</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>459</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="K103" s="6"/>
       <c r="L103" s="6"/>
       <c r="M103" s="6">
         <v>10</v>
@@ -5698,17 +5131,17 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>242</v>
+        <v>389</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>293</v>
+        <v>127</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>294</v>
+        <v>128</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G104" s="9">
         <v>1972</v>
@@ -5716,9 +5149,7 @@
       <c r="H104" s="10"/>
       <c r="I104" s="10"/>
       <c r="J104" s="10"/>
-      <c r="K104" s="10" t="s">
-        <v>460</v>
-      </c>
+      <c r="K104" s="10"/>
       <c r="L104" s="10"/>
       <c r="M104" s="9">
         <v>10</v>
@@ -5729,31 +5160,29 @@
         <v>104</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G105" s="6">
         <v>1983</v>
       </c>
       <c r="H105" s="6"/>
       <c r="I105" s="6" t="s">
-        <v>54</v>
+        <v>351</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>461</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="K105" s="6"/>
       <c r="L105" s="6"/>
       <c r="M105" s="6">
         <v>10</v>
@@ -5764,17 +5193,17 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>241</v>
+        <v>391</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>295</v>
+        <v>129</v>
       </c>
       <c r="E106" s="9"/>
       <c r="F106" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G106" s="9">
         <v>1983</v>
@@ -5782,9 +5211,7 @@
       <c r="H106" s="10"/>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
-      <c r="K106" s="10" t="s">
-        <v>462</v>
-      </c>
+      <c r="K106" s="10"/>
       <c r="L106" s="10"/>
       <c r="M106" s="9">
         <v>10</v>
@@ -5795,31 +5222,29 @@
         <v>106</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G107" s="6">
         <v>1996</v>
       </c>
       <c r="H107" s="6"/>
       <c r="I107" s="6" t="s">
-        <v>55</v>
+        <v>353</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>463</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="K107" s="6"/>
       <c r="L107" s="6"/>
       <c r="M107" s="6">
         <v>10</v>
@@ -5830,17 +5255,17 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>243</v>
+        <v>393</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>296</v>
+        <v>130</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="E108" s="9"/>
       <c r="F108" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G108" s="9">
         <v>1996</v>
@@ -5848,9 +5273,7 @@
       <c r="H108" s="10"/>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
-      <c r="K108" s="10" t="s">
-        <v>464</v>
-      </c>
+      <c r="K108" s="10"/>
       <c r="L108" s="10"/>
       <c r="M108" s="9">
         <v>10</v>
@@ -5861,31 +5284,29 @@
         <v>108</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G109" s="6">
         <v>2002</v>
       </c>
       <c r="H109" s="6"/>
       <c r="I109" s="6" t="s">
-        <v>55</v>
+        <v>353</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="K109" s="6" t="s">
-        <v>465</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="K109" s="6"/>
       <c r="L109" s="6"/>
       <c r="M109" s="6">
         <v>10</v>
@@ -5896,31 +5317,29 @@
         <v>109</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>184</v>
+        <v>275</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G110" s="6">
         <v>2007</v>
       </c>
       <c r="H110" s="6"/>
       <c r="I110" s="6" t="s">
-        <v>59</v>
+        <v>361</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>466</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="K110" s="6"/>
       <c r="L110" s="6"/>
       <c r="M110" s="6">
         <v>10</v>
@@ -5931,31 +5350,29 @@
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>85</v>
+        <v>396</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G111" s="6">
         <v>2012</v>
       </c>
       <c r="H111" s="6"/>
       <c r="I111" s="6" t="s">
-        <v>59</v>
+        <v>361</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="K111" s="6" t="s">
-        <v>467</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="K111" s="6"/>
       <c r="L111" s="6"/>
       <c r="M111" s="6">
         <v>10</v>
@@ -5966,31 +5383,29 @@
         <v>111</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>87</v>
+        <v>397</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G112" s="6">
         <v>2003</v>
       </c>
       <c r="H112" s="6"/>
       <c r="I112" s="6" t="s">
-        <v>60</v>
+        <v>363</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="K112" s="6" t="s">
-        <v>468</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="K112" s="6"/>
       <c r="L112" s="6"/>
       <c r="M112" s="6">
         <v>10</v>
@@ -6001,31 +5416,29 @@
         <v>112</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>89</v>
+        <v>398</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G113" s="6">
         <v>2007</v>
       </c>
       <c r="H113" s="6"/>
       <c r="I113" s="6" t="s">
-        <v>60</v>
+        <v>363</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="K113" s="6" t="s">
-        <v>469</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="K113" s="6"/>
       <c r="L113" s="6"/>
       <c r="M113" s="6">
         <v>10</v>
@@ -6036,29 +5449,27 @@
         <v>113</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>91</v>
+        <v>399</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6" t="s">
-        <v>62</v>
+        <v>367</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>470</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="K114" s="6"/>
       <c r="L114" s="6"/>
       <c r="M114" s="6">
         <v>10</v>
@@ -6069,29 +5480,27 @@
         <v>114</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>93</v>
+        <v>400</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>184</v>
+        <v>275</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="E115" s="6"/>
       <c r="F115" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6" t="s">
-        <v>62</v>
+        <v>367</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>471</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="K115" s="6"/>
       <c r="L115" s="6"/>
       <c r="M115" s="6">
         <v>10</v>
@@ -6102,31 +5511,29 @@
         <v>115</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>94</v>
+        <v>401</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="E116" s="6"/>
       <c r="F116" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G116" s="6">
         <v>2004</v>
       </c>
       <c r="H116" s="6"/>
       <c r="I116" s="6" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>472</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="K116" s="6"/>
       <c r="L116" s="6"/>
       <c r="M116" s="6">
         <v>10</v>
@@ -6137,29 +5544,27 @@
         <v>116</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>96</v>
+        <v>402</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="E117" s="6"/>
       <c r="F117" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="K117" s="6" t="s">
-        <v>473</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="K117" s="6"/>
       <c r="L117" s="6"/>
       <c r="M117" s="6">
         <v>10</v>
@@ -6170,29 +5575,27 @@
         <v>117</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>97</v>
+        <v>403</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="K118" s="6" t="s">
-        <v>474</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="K118" s="6"/>
       <c r="L118" s="6"/>
       <c r="M118" s="6">
         <v>10</v>
@@ -6203,31 +5606,29 @@
         <v>118</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>98</v>
+        <v>404</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G119" s="6">
         <v>2009</v>
       </c>
       <c r="H119" s="6"/>
       <c r="I119" s="6" t="s">
-        <v>66</v>
+        <v>374</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="K119" s="6" t="s">
-        <v>475</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="K119" s="6"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6">
         <v>11</v>
@@ -6238,31 +5639,29 @@
         <v>119</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>99</v>
+        <v>405</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G120" s="6">
         <v>2019</v>
       </c>
       <c r="H120" s="6"/>
       <c r="I120" s="6" t="s">
-        <v>66</v>
+        <v>374</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="K120" s="6" t="s">
-        <v>476</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="K120" s="6"/>
       <c r="L120" s="6"/>
       <c r="M120" s="6">
         <v>11</v>
@@ -6273,31 +5672,29 @@
         <v>120</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>100</v>
+        <v>406</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G121" s="6">
         <v>2015</v>
       </c>
       <c r="H121" s="6"/>
       <c r="I121" s="6" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="K121" s="6" t="s">
-        <v>477</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="K121" s="6"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6">
         <v>11</v>
@@ -6308,31 +5705,29 @@
         <v>121</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>102</v>
+        <v>407</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>190</v>
+        <v>278</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G122" s="6">
         <v>2026</v>
       </c>
       <c r="H122" s="6"/>
       <c r="I122" s="6" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="K122" s="6" t="s">
-        <v>478</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="K122" s="6"/>
       <c r="L122" s="6"/>
       <c r="M122" s="6">
         <v>11</v>
@@ -6343,31 +5738,29 @@
         <v>122</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G123" s="6">
         <v>2015</v>
       </c>
       <c r="H123" s="6"/>
       <c r="I123" s="6" t="s">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="K123" s="6" t="s">
-        <v>479</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="K123" s="6"/>
       <c r="L123" s="6"/>
       <c r="M123" s="6">
         <v>11</v>
@@ -6378,31 +5771,29 @@
         <v>123</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>105</v>
+        <v>409</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G124" s="6">
         <v>2017</v>
       </c>
       <c r="H124" s="6"/>
       <c r="I124" s="6" t="s">
-        <v>70</v>
+        <v>379</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="K124" s="6" t="s">
-        <v>480</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="K124" s="6"/>
       <c r="L124" s="6"/>
       <c r="M124" s="6">
         <v>11</v>
@@ -6413,31 +5804,29 @@
         <v>124</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>106</v>
+        <v>410</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G125" s="6">
         <v>2003</v>
       </c>
       <c r="H125" s="6"/>
       <c r="I125" s="6" t="s">
-        <v>76</v>
+        <v>386</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="K125" s="6" t="s">
-        <v>481</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="K125" s="6"/>
       <c r="L125" s="6"/>
       <c r="M125" s="6">
         <v>11</v>
@@ -6448,31 +5837,29 @@
         <v>125</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G126" s="6">
         <v>2007</v>
       </c>
       <c r="H126" s="6"/>
       <c r="I126" s="6" t="s">
-        <v>76</v>
+        <v>386</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>482</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="K126" s="6"/>
       <c r="L126" s="6"/>
       <c r="M126" s="6">
         <v>11</v>
@@ -6483,17 +5870,17 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>304</v>
+        <v>135</v>
       </c>
       <c r="E127" s="9"/>
       <c r="F127" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G127" s="9">
         <v>2005</v>
@@ -6501,9 +5888,7 @@
       <c r="H127" s="10"/>
       <c r="I127" s="10"/>
       <c r="J127" s="10"/>
-      <c r="K127" s="13" t="s">
-        <v>483</v>
-      </c>
+      <c r="K127" s="13"/>
       <c r="L127" s="10"/>
       <c r="M127" s="9">
         <v>11</v>
@@ -6514,31 +5899,29 @@
         <v>127</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>109</v>
+        <v>411</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G128" s="6">
         <v>2009</v>
       </c>
       <c r="H128" s="6"/>
       <c r="I128" s="6" t="s">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="J128" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="K128" s="6" t="s">
-        <v>484</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="K128" s="6"/>
       <c r="L128" s="6"/>
       <c r="M128" s="6">
         <v>11</v>
@@ -6549,31 +5932,29 @@
         <v>128</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>111</v>
+        <v>412</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G129" s="6">
         <v>2014</v>
       </c>
       <c r="H129" s="6"/>
       <c r="I129" s="6" t="s">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="K129" s="6" t="s">
-        <v>485</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="K129" s="6"/>
       <c r="L129" s="6"/>
       <c r="M129" s="6">
         <v>11</v>
@@ -6584,31 +5965,29 @@
         <v>129</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>112</v>
+        <v>413</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G130" s="6">
         <v>2021</v>
       </c>
       <c r="H130" s="6"/>
       <c r="I130" s="6" t="s">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="K130" s="6" t="s">
-        <v>486</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="K130" s="6"/>
       <c r="L130" s="6"/>
       <c r="M130" s="6">
         <v>11</v>
@@ -6619,31 +5998,29 @@
         <v>130</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>114</v>
+        <v>414</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G131" s="6">
         <v>2023</v>
       </c>
       <c r="H131" s="6"/>
       <c r="I131" s="6" t="s">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="J131" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="K131" s="6" t="s">
-        <v>487</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="K131" s="6"/>
       <c r="L131" s="6"/>
       <c r="M131" s="6">
         <v>11</v>
@@ -6657,7 +6034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D7B4B2-F481-4665-8571-03674889C862}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -6668,480 +6045,104 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>318</v>
+        <v>144</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>319</v>
+        <v>145</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>320</v>
+        <v>146</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>321</v>
+        <v>147</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>322</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>328</v>
+        <v>175</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>6</v>
+        <v>284</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>9</v>
+        <v>285</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E2" s="7"/>
+        <v>157</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>329</v>
+        <v>176</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E3" s="7"/>
+        <v>157</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>334</v>
+        <v>177</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>16</v>
+        <v>287</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>199</v>
+        <v>288</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E4" s="7"/>
+        <v>157</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>335</v>
+        <v>178</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E5" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>353</v>
+        <v>179</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>29</v>
+        <v>291</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="24" t="str">
-        <f>B7&amp;"S1"</f>
-        <v>VA-6.05S1</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>331</v>
+        <v>157</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -7164,39 +6165,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>324</v>
+        <v>150</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>382</v>
+        <v>183</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>325</v>
+        <v>151</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>380</v>
+        <v>181</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>530</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>6</v>
+        <v>292</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>379</v>
+        <v>180</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>494</v>
+        <v>417</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -7204,19 +6205,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>492</v>
+        <v>194</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>493</v>
+        <v>195</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F3" s="7">
         <v>2</v>
@@ -7224,19 +6225,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>534</v>
+        <v>225</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>535</v>
+        <v>418</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F4" s="7">
         <v>3</v>
@@ -7244,19 +6245,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>22</v>
+        <v>302</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>528</v>
+        <v>219</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>529</v>
+        <v>220</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F5" s="7">
         <v>4</v>
@@ -7264,19 +6265,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>310</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>503</v>
+        <v>203</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>504</v>
+        <v>419</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F6" s="7">
         <v>5</v>
@@ -7284,19 +6285,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>522</v>
+        <v>215</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>523</v>
+        <v>216</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>524</v>
+        <v>217</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F7" s="7">
         <v>6</v>
@@ -7304,19 +6305,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>384</v>
+        <v>185</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>511</v>
+        <v>420</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F8" s="7">
         <v>7</v>
@@ -7324,19 +6325,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>207</v>
+        <v>318</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>383</v>
+        <v>184</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>491</v>
+        <v>193</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F9" s="7">
         <v>8</v>
@@ -7344,19 +6345,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>49</v>
+        <v>341</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>385</v>
+        <v>186</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>506</v>
+        <v>421</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F10" s="7">
         <v>9</v>
@@ -7364,19 +6365,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>386</v>
+        <v>187</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>519</v>
+        <v>212</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F11" s="7">
         <v>10</v>
@@ -7384,19 +6385,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>65</v>
+        <v>373</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>327</v>
+        <v>153</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F12" s="7">
         <v>11</v>
@@ -7404,19 +6405,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>42</v>
+        <v>328</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>490</v>
+        <v>192</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>508</v>
+        <v>205</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F13" s="7">
         <v>12</v>
@@ -7424,19 +6425,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>495</v>
+        <v>196</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>496</v>
+        <v>416</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F14" s="7">
         <v>13</v>
@@ -7444,19 +6445,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>507</v>
+        <v>204</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>518</v>
+        <v>422</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F15" s="7">
         <v>14</v>
@@ -7464,19 +6465,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>533</v>
+        <v>224</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>532</v>
+        <v>223</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F16" s="7">
         <v>15</v>
@@ -7484,19 +6485,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>38</v>
+        <v>321</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>509</v>
+        <v>206</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>510</v>
+        <v>423</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F17" s="7">
         <v>16</v>
@@ -7504,19 +6505,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>512</v>
+        <v>207</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>513</v>
+        <v>424</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F18" s="7">
         <v>17</v>
@@ -7524,19 +6525,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>514</v>
-      </c>
       <c r="D19" s="7" t="s">
-        <v>517</v>
+        <v>211</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F19" s="7">
         <v>18</v>
@@ -7544,19 +6545,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>213</v>
+        <v>331</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>515</v>
+        <v>209</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>516</v>
+        <v>210</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F20" s="7">
         <v>19</v>
@@ -7564,19 +6565,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>326</v>
+        <v>152</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>540</v>
+        <v>230</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>541</v>
+        <v>231</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="F21" s="27">
         <v>20</v>
@@ -7606,36 +6607,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="B1" t="s">
-        <v>337</v>
+        <v>159</v>
       </c>
       <c r="C1" t="s">
-        <v>338</v>
+        <v>160</v>
       </c>
       <c r="D1" t="s">
-        <v>339</v>
+        <v>161</v>
       </c>
       <c r="E1" t="s">
-        <v>340</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>349</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
-        <v>352</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -7645,7 +6646,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2870D094-0F04-43A9-85F0-3281621B51DF}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -7657,274 +6658,121 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>344</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>387</v>
+        <v>188</v>
       </c>
       <c r="C1" t="s">
-        <v>345</v>
+        <v>167</v>
       </c>
       <c r="D1" t="s">
-        <v>388</v>
+        <v>189</v>
       </c>
       <c r="E1" t="s">
-        <v>346</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="B2" t="s">
-        <v>389</v>
+        <v>190</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>544</v>
+        <v>233</v>
       </c>
       <c r="D2" t="s">
-        <v>547</v>
+        <v>234</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="B3" t="s">
-        <v>389</v>
+        <v>190</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>446</v>
+        <v>376</v>
       </c>
       <c r="D3" t="s">
-        <v>390</v>
+        <v>191</v>
       </c>
       <c r="E3" t="s">
-        <v>348</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>68</v>
+      <c r="A4" s="31" t="s">
+        <v>284</v>
       </c>
       <c r="B4" t="s">
-        <v>389</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>543</v>
+        <v>190</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>546</v>
+        <v>237</v>
       </c>
       <c r="E4" t="s">
-        <v>347</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>66</v>
+      <c r="A5" s="31" t="s">
+        <v>284</v>
       </c>
       <c r="B5" t="s">
-        <v>389</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>444</v>
+        <v>190</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>238</v>
       </c>
       <c r="D5" t="s">
-        <v>390</v>
+        <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>348</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>42</v>
+      <c r="A6" s="31" t="s">
+        <v>284</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>488</v>
+        <v>190</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>239</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>242</v>
       </c>
       <c r="E6" t="s">
-        <v>347</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>68</v>
+      <c r="A7" s="31" t="s">
+        <v>284</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>548</v>
+        <v>190</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>240</v>
       </c>
       <c r="D7" t="s">
-        <v>546</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>389</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="D8" t="s">
-        <v>546</v>
-      </c>
-      <c r="E8" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" t="s">
-        <v>389</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>551</v>
-      </c>
-      <c r="D9" t="s">
-        <v>552</v>
-      </c>
-      <c r="E9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" t="s">
-        <v>389</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="D10" t="s">
-        <v>550</v>
-      </c>
-      <c r="E10" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" t="s">
-        <v>389</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="D11" t="s">
-        <v>558</v>
-      </c>
-      <c r="E11" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" t="s">
-        <v>389</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="D12" t="s">
-        <v>557</v>
-      </c>
-      <c r="E12" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>389</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>566</v>
-      </c>
-      <c r="D13" t="s">
-        <v>559</v>
-      </c>
-      <c r="E13" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>389</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>560</v>
-      </c>
-      <c r="D14" t="s">
-        <v>563</v>
-      </c>
-      <c r="E14" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>389</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>561</v>
-      </c>
-      <c r="D15" t="s">
-        <v>564</v>
-      </c>
-      <c r="E15" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>389</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>562</v>
-      </c>
-      <c r="D16" t="s">
-        <v>565</v>
-      </c>
-      <c r="E16" t="s">
-        <v>348</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
